--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -3869,7 +3869,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>R1_MAP_Basic_Anchor</t>
+          <t>R01_MAP_Basic</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>TestScene에는 앵커가 없음. 방 모델(R01_Serface 아래 O0085_Floor, O0086_North_wall …)이 씬에 직접 놓여 있어 스폰하지 않음</t>
+          <t>Ingame 씬의 1번 방 최상위 오브젝트 R01_MAP_Basic (앵커 아님, 안에 R01_Serface · R01_Other 프리팹). 스폰하지 않음</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>R1A_SPAWN</t>
+          <t>R01A_SPAWN</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>시작 위치 미지정</t>
+          <t>Ingame 시작 위치 오브젝트 (Unity 이름 R1A_SPAWN → R01A_SPAWN으로 바꿈, 사용자 결정). 스폰할 프리팹 13001이 아직 없어 꺼 둠</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>R1B_SPAWN</t>
+          <t>R01B_SPAWN</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>시작 위치 미지정</t>
+          <t>A와 같은 규칙으로 이름만 맞춤. Unity에 아직 없음, 시작 위치 미지정</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">

--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -2814,11 +2814,11 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>13036</v>
+        <v>13002</v>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>공통문. 출구, 방 ExitRule대로 열림</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 문 프리팹 Door (모든 방 공통)</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -3735,7 +3735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>A만 단서. 카드 50장이 이 프리팹 하나에 들어 있음</t>
+          <t>옛 카드 자리. SILENT_Room_01_Final 기준 R01A_CardsPoint(2237)로 대체 (CARD 3001~3050도 2237로 옮김)</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>R01A_SPAWN</t>
+          <t>R01A_Player</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Ingame 시작 위치 오브젝트 (Unity 이름 R1A_SPAWN → R01A_SPAWN으로 바꿈, 사용자 결정). 스폰할 프리팹 13001이 아직 없어 꺼 둠</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 R01A_Player (사용자가 직접 배치, 2026-10-20). 프리팹 13001 경로는 아직 예시라 실제 플레이어 시작 프리팹이 필요함</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>R01B_SPAWN</t>
+          <t>R01B_Player</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
@@ -4237,26 +4237,26 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>A와 같은 규칙으로 이름만 맞춤. Unity에 아직 없음, 시작 위치 미지정</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01B 아래 R01B_Player (사용자가 직접 배치, 2026-10-20). 프리팹 13001 경로는 아직 예시라 실제 플레이어 시작 프리팹이 필요함</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>2033</v>
+        <v>2237</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 테이블</t>
+          <t>A 1번 방 바닥 카드</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
@@ -4265,13 +4265,17 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>R02_A_TablePoint</t>
+          <t>R01A_CardsPoint</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>13052</v>
-      </c>
-      <c r="G18" s="8" t="n"/>
+        <v>13067</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴</t>
+        </is>
+      </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4280,30 +4284,34 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>2035</v>
+        <v>2238</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 글자 표시판</t>
+          <t>1번 방 천장 (A·B 공통)</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>R2A_SIGN</t>
+          <t>R01_CeilingPoint</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G19" s="8" t="n"/>
+        <v>13068</v>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
+        </is>
+      </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4312,68 +4320,68 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2125</v>
+        <v>2239</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 01</t>
+          <t>1번 방 바닥·벽 (A·B 공통)</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>R02_RedFramePoint_1</t>
+          <t>R01_StructurePoint</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>13063</v>
+        <v>13069</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>색 Red</t>
+          <t>바닥·벽은 방 프리팹(Room_01_Final, PREFAB 13020/13027) 자체라 따로 스폰하지 않음. 앵커 오브젝트는 프리팹 안에 남아 있음</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2126</v>
+        <v>2240</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 02</t>
+          <t>1번 방 문 막기용 문 dver' (A·B 공통)</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>R02_RedFramePoint_2</t>
+          <t>R01_DverPoint</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>13063</v>
+        <v>13070</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>색 Red</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -4384,32 +4392,32 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2127</v>
+        <v>2241</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 03</t>
+          <t>1번 방 서랍장 (A·B 공통)</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>R02_BlueFramePoint_2</t>
+          <t>R01_DrawerPoint</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>13056</v>
+        <v>13071</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>색 Blue</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -4420,11 +4428,11 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2128</v>
+        <v>2033</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 04</t>
+          <t>A 2번 방 테이블</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -4432,22 +4440,18 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_4</t>
+          <t>R02_A_TablePoint</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>13064</v>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>색 Yellow</t>
-        </is>
-      </c>
+        <v>13052</v>
+      </c>
+      <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4456,11 +4460,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2129</v>
+        <v>2035</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 05</t>
+          <t>A 2번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -4468,22 +4472,18 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_1</t>
+          <t>R2A_SIGN</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13058</v>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>색 Green</t>
-        </is>
-      </c>
+        <v>13008</v>
+      </c>
+      <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4492,11 +4492,11 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 06</t>
+          <t>B 2번 방 액자 01</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -4509,15 +4509,15 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_2</t>
+          <t>R02_RedFramePoint_1</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>13058</v>
+        <v>13063</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>색 Green. Unity 이름에 공백('R02_GreenFramePoint _2'), 표에는 공백 없이 씀</t>
+          <t>색 Red</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -4528,11 +4528,11 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 07</t>
+          <t>B 2번 방 액자 02</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -4545,15 +4545,15 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_3</t>
+          <t>R02_RedFramePoint_2</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13058</v>
+        <v>13063</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>색 Green</t>
+          <t>색 Red</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -4564,11 +4564,11 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 08</t>
+          <t>B 2번 방 액자 03</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -4581,15 +4581,15 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_4</t>
+          <t>R02_BlueFramePoint_2</t>
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>13058</v>
+        <v>13056</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>색 Green</t>
+          <t>색 Blue</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -4600,11 +4600,11 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 09</t>
+          <t>B 2번 방 액자 04</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -4617,15 +4617,15 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>R02_BlackFramePoint_2</t>
+          <t>R02_YellowFramePoint_4</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>13055</v>
+        <v>13064</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>색 Black</t>
+          <t>색 Yellow</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -4636,11 +4636,11 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 10</t>
+          <t>B 2번 방 액자 05</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -4653,15 +4653,15 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_3</t>
+          <t>R02_GreenFramePoint_1</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>13062</v>
+        <v>13058</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>색 Green</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -4672,11 +4672,11 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>2135</v>
+        <v>2130</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 11</t>
+          <t>B 2번 방 액자 06</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -4689,15 +4689,15 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_4</t>
+          <t>R02_GreenFramePoint_2</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>13062</v>
+        <v>13058</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>색 Green. Unity 이름에 공백('R02_GreenFramePoint _2'), 표에는 공백 없이 씀</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -4708,11 +4708,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>2136</v>
+        <v>2131</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 12</t>
+          <t>B 2번 방 액자 07</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -4725,15 +4725,15 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_2</t>
+          <t>R02_GreenFramePoint_3</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>13060</v>
+        <v>13058</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>색 Navy</t>
+          <t>색 Green</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -4744,11 +4744,11 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>2137</v>
+        <v>2132</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 13</t>
+          <t>B 2번 방 액자 08</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -4761,15 +4761,15 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_3</t>
+          <t>R02_GreenFramePoint_4</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>13060</v>
+        <v>13058</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>색 Navy</t>
+          <t>색 Green</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -4780,11 +4780,11 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>2138</v>
+        <v>2133</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 14</t>
+          <t>B 2번 방 액자 09</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -4797,15 +4797,15 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>R02_BlueFramePoint_1</t>
+          <t>R02_BlackFramePoint_2</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>13056</v>
+        <v>13055</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>색 Blue</t>
+          <t>색 Black</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -4816,11 +4816,11 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>2139</v>
+        <v>2134</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 15</t>
+          <t>B 2번 방 액자 10</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -4833,15 +4833,15 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>R02_GrayFramePoint_1</t>
+          <t>R02_PuppleFreamPoint_3</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>13057</v>
+        <v>13062</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>색 Gray</t>
+          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -4852,11 +4852,11 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>2140</v>
+        <v>2135</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 16</t>
+          <t>B 2번 방 액자 11</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -4869,15 +4869,15 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>R02_GrayFramePoint_2</t>
+          <t>R02_PuppleFreamPoint_4</t>
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>13057</v>
+        <v>13062</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>색 Gray</t>
+          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -4888,11 +4888,11 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>2141</v>
+        <v>2136</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 17</t>
+          <t>B 2번 방 액자 12</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -4905,15 +4905,15 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_1</t>
+          <t>R02_NavyFreamPoint_2</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>13064</v>
+        <v>13060</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>색 Navy</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -4924,11 +4924,11 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>2142</v>
+        <v>2137</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 18</t>
+          <t>B 2번 방 액자 13</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -4941,15 +4941,15 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_2</t>
+          <t>R02_NavyFreamPoint_3</t>
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>13064</v>
+        <v>13060</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>색 Navy</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -4960,11 +4960,11 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>2143</v>
+        <v>2138</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 19</t>
+          <t>B 2번 방 액자 14</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -4977,15 +4977,15 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_3</t>
+          <t>R02_BlueFramePoint_1</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>13064</v>
+        <v>13056</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>색 Blue</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -4996,11 +4996,11 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>2144</v>
+        <v>2139</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 20</t>
+          <t>B 2번 방 액자 15</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -5013,15 +5013,15 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>R02_OrangeFreamPoint_1</t>
+          <t>R02_GrayFramePoint_1</t>
         </is>
       </c>
       <c r="F39" s="8" t="n">
-        <v>13061</v>
+        <v>13057</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>색 Orange</t>
+          <t>색 Gray</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -5032,11 +5032,11 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 21</t>
+          <t>B 2번 방 액자 16</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -5049,15 +5049,15 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>R02_OrangeFreamPoint_2</t>
+          <t>R02_GrayFramePoint_2</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>13061</v>
+        <v>13057</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>색 Orange</t>
+          <t>색 Gray</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -5068,11 +5068,11 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 22</t>
+          <t>B 2번 방 액자 17</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -5085,15 +5085,15 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>R02_BlackFramePoint_1</t>
+          <t>R02_YellowFramePoint_1</t>
         </is>
       </c>
       <c r="F41" s="8" t="n">
-        <v>13055</v>
+        <v>13064</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>색 Black</t>
+          <t>색 Yellow</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -5104,11 +5104,11 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>2147</v>
+        <v>2142</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 23</t>
+          <t>B 2번 방 액자 18</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -5121,15 +5121,15 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_1</t>
+          <t>R02_YellowFramePoint_2</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>13062</v>
+        <v>13064</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>색 Yellow</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -5140,11 +5140,11 @@
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>2148</v>
+        <v>2143</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 24</t>
+          <t>B 2번 방 액자 19</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -5157,15 +5157,15 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_2</t>
+          <t>R02_YellowFramePoint_3</t>
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>13062</v>
+        <v>13064</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>색 Yellow</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -5176,11 +5176,11 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 25</t>
+          <t>B 2번 방 액자 20</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -5193,15 +5193,15 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>R02_MintFramePoint_1</t>
+          <t>R02_OrangeFreamPoint_1</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>13059</v>
+        <v>13061</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
+          <t>색 Orange</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -5212,11 +5212,11 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 26</t>
+          <t>B 2번 방 액자 21</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -5229,15 +5229,15 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>R02_MintFramePoint_2</t>
+          <t>R02_OrangeFreamPoint_2</t>
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>13059</v>
+        <v>13061</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
+          <t>색 Orange</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -5248,11 +5248,11 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>2152</v>
+        <v>2146</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 28</t>
+          <t>B 2번 방 액자 22</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -5265,15 +5265,15 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_1</t>
+          <t>R02_BlackFramePoint_1</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>13060</v>
+        <v>13055</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>색 Navy</t>
+          <t>색 Black</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -5284,15 +5284,15 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>2040</v>
+        <v>2147</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 글자 표시판</t>
+          <t>B 2번 방 액자 23</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
@@ -5301,13 +5301,17 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>R3B_SIGN</t>
+          <t>R02_PuppleFreamPoint_1</t>
         </is>
       </c>
       <c r="F47" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G47" s="8" t="n"/>
+        <v>13062</v>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+        </is>
+      </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5316,32 +5320,32 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>2183</v>
+        <v>2148</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 01</t>
+          <t>B 2번 방 액자 24</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_01</t>
+          <t>R02_PuppleFreamPoint_2</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>13011</v>
+        <v>13062</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
+          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -5352,32 +5356,32 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>2184</v>
+        <v>2149</v>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 02</t>
+          <t>B 2번 방 액자 25</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_02</t>
+          <t>R02_MintFramePoint_1</t>
         </is>
       </c>
       <c r="F49" s="8" t="n">
-        <v>13011</v>
+        <v>13059</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
+          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -5388,32 +5392,32 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>2185</v>
+        <v>2150</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 03</t>
+          <t>B 2번 방 액자 26</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_03</t>
+          <t>R02_MintFramePoint_2</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>13011</v>
+        <v>13059</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
+          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -5424,32 +5428,32 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>2186</v>
+        <v>2152</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 04</t>
+          <t>B 2번 방 액자 28</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_04</t>
+          <t>R02_NavyFreamPoint_1</t>
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>13011</v>
+        <v>13060</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
+          <t>색 Navy</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -5460,11 +5464,11 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>2187</v>
+        <v>2040</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 05</t>
+          <t>B 3번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -5472,22 +5476,18 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_05</t>
+          <t>R3B_SIGN</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>13011</v>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
-        </is>
-      </c>
+        <v>13008</v>
+      </c>
+      <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5496,11 +5496,11 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 06</t>
+          <t>A 3번 방 단서 화살표 01</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_06</t>
+          <t>R3A_ARROW_01</t>
         </is>
       </c>
       <c r="F53" s="8" t="n">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -5532,11 +5532,11 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 07</t>
+          <t>A 3번 방 단서 화살표 02</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_07</t>
+          <t>R3A_ARROW_02</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -5568,11 +5568,11 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>2190</v>
+        <v>2185</v>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 08</t>
+          <t>A 3번 방 단서 화살표 03</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_08</t>
+          <t>R3A_ARROW_03</t>
         </is>
       </c>
       <c r="F55" s="8" t="n">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -5604,11 +5604,11 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 09</t>
+          <t>A 3번 방 단서 화살표 04</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_09</t>
+          <t>R3A_ARROW_04</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -5640,11 +5640,11 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 10</t>
+          <t>A 3번 방 단서 화살표 05</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_10</t>
+          <t>R3A_ARROW_05</t>
         </is>
       </c>
       <c r="F57" s="8" t="n">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -5676,15 +5676,15 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>2041</v>
+        <v>2188</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 테이블</t>
+          <t>A 3번 방 단서 화살표 06</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
@@ -5693,13 +5693,17 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>R4A_TABLE</t>
+          <t>R3A_ARROW_06</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>13003</v>
-      </c>
-      <c r="G58" s="8" t="n"/>
+        <v>13011</v>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
+        </is>
+      </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5708,15 +5712,15 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>2043</v>
+        <v>2189</v>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 글자 표시판</t>
+          <t>A 3번 방 단서 화살표 07</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
@@ -5725,13 +5729,17 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>R4A_SIGN</t>
+          <t>R3A_ARROW_07</t>
         </is>
       </c>
       <c r="F59" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G59" s="8" t="n"/>
+        <v>13011</v>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
+        </is>
+      </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5740,32 +5748,32 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>2074</v>
+        <v>2190</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 배선 콘솔 받침대</t>
+          <t>A 3번 방 단서 화살표 08</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>R4B_CONSOLE_STAND</t>
+          <t>R3A_ARROW_08</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>13019</v>
+        <v>13011</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -5776,32 +5784,32 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>2153</v>
+        <v>2191</v>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 01 (정답)</t>
+          <t>A 3번 방 단서 화살표 09</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_01</t>
+          <t>R3A_ARROW_09</t>
         </is>
       </c>
       <c r="F61" s="8" t="n">
-        <v>13034</v>
+        <v>13011</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -5812,32 +5820,32 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>2154</v>
+        <v>2192</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 02 (정답)</t>
+          <t>A 3번 방 단서 화살표 10</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_02</t>
+          <t>R3A_ARROW_10</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>13034</v>
+        <v>13011</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -5848,11 +5856,11 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>2155</v>
+        <v>2041</v>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 03 (정답)</t>
+          <t>A 4번 방 테이블</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -5860,22 +5868,18 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_03</t>
+          <t>R4A_TABLE</t>
         </is>
       </c>
       <c r="F63" s="8" t="n">
-        <v>13034</v>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>배선 콘솔 안 단자에 연결</t>
-        </is>
-      </c>
+        <v>13003</v>
+      </c>
+      <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5884,11 +5888,11 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>2156</v>
+        <v>2043</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 04 (정답)</t>
+          <t>A 4번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -5896,22 +5900,18 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_04</t>
+          <t>R4A_SIGN</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>13034</v>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>배선 콘솔 안 단자에 연결</t>
-        </is>
-      </c>
+        <v>13008</v>
+      </c>
+      <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5920,11 +5920,11 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>2157</v>
+        <v>2074</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 05 (정답)</t>
+          <t>B 4번 방 배선 콘솔 받침대</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -5937,15 +5937,15 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_05</t>
+          <t>R4B_CONSOLE_STAND</t>
         </is>
       </c>
       <c r="F65" s="8" t="n">
-        <v>13034</v>
+        <v>13019</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -5956,11 +5956,11 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 06 (가짜)</t>
+          <t>B 4번 방 전선 01 (정답)</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_06</t>
+          <t>R4B_WIRE_01</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
@@ -5992,11 +5992,11 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 07 (가짜)</t>
+          <t>B 4번 방 전선 02 (정답)</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_07</t>
+          <t>R4B_WIRE_02</t>
         </is>
       </c>
       <c r="F67" s="8" t="n">
@@ -6028,11 +6028,11 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 08 (가짜)</t>
+          <t>B 4번 방 전선 03 (정답)</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_08</t>
+          <t>R4B_WIRE_03</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
@@ -6064,11 +6064,11 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>2161</v>
+        <v>2156</v>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 09 (가짜)</t>
+          <t>B 4번 방 전선 04 (정답)</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_09</t>
+          <t>R4B_WIRE_04</t>
         </is>
       </c>
       <c r="F69" s="8" t="n">
@@ -6100,11 +6100,11 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>2162</v>
+        <v>2157</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 10 (가짜)</t>
+          <t>B 4번 방 전선 05 (정답)</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_10</t>
+          <t>R4B_WIRE_05</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
@@ -6136,30 +6136,34 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>2048</v>
+        <v>2158</v>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 테이블</t>
+          <t>B 4번 방 전선 06 (가짜)</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>R5A_TABLE</t>
+          <t>R4B_WIRE_06</t>
         </is>
       </c>
       <c r="F71" s="8" t="n">
-        <v>13003</v>
-      </c>
-      <c r="G71" s="8" t="n"/>
+        <v>13034</v>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>배선 콘솔 안 단자에 연결</t>
+        </is>
+      </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6168,30 +6172,34 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>2049</v>
+        <v>2159</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 종이</t>
+          <t>B 4번 방 전선 07 (가짜)</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>R5A_PAPER</t>
+          <t>R4B_WIRE_07</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>13016</v>
-      </c>
-      <c r="G72" s="8" t="n"/>
+        <v>13034</v>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>배선 콘솔 안 단자에 연결</t>
+        </is>
+      </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6200,15 +6208,15 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>2050</v>
+        <v>2160</v>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 자물쇠 받침대</t>
+          <t>B 4번 방 전선 08 (가짜)</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
@@ -6217,13 +6225,17 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>R5B_STAND</t>
+          <t>R4B_WIRE_08</t>
         </is>
       </c>
       <c r="F73" s="8" t="n">
-        <v>13004</v>
-      </c>
-      <c r="G73" s="8" t="n"/>
+        <v>13034</v>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>배선 콘솔 안 단자에 연결</t>
+        </is>
+      </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6232,15 +6244,15 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>2052</v>
+        <v>2161</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 글자 표시판</t>
+          <t>B 4번 방 전선 09 (가짜)</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
@@ -6249,13 +6261,17 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>R5B_SIGN</t>
+          <t>R4B_WIRE_09</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G74" s="8" t="n"/>
+        <v>13034</v>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>배선 콘솔 안 단자에 연결</t>
+        </is>
+      </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6264,30 +6280,34 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 01 (진짜 정의)</t>
+          <t>B 4번 방 전선 10 (가짜)</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_01</t>
+          <t>R4B_WIRE_10</t>
         </is>
       </c>
       <c r="F75" s="8" t="n">
-        <v>13014</v>
-      </c>
-      <c r="G75" s="8" t="n"/>
+        <v>13034</v>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>배선 콘솔 안 단자에 연결</t>
+        </is>
+      </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6296,11 +6316,11 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>2164</v>
+        <v>2048</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 02</t>
+          <t>A 5번 방 테이블</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
@@ -6313,11 +6333,11 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_02</t>
+          <t>R5A_TABLE</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>13014</v>
+        <v>13003</v>
       </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="inlineStr">
@@ -6328,11 +6348,11 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>2165</v>
+        <v>2049</v>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 03</t>
+          <t>A 5번 방 종이</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -6345,11 +6365,11 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_03</t>
+          <t>R5A_PAPER</t>
         </is>
       </c>
       <c r="F77" s="8" t="n">
-        <v>13014</v>
+        <v>13016</v>
       </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
@@ -6360,11 +6380,11 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>2166</v>
+        <v>2050</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 04</t>
+          <t>B 5번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -6372,16 +6392,16 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_04</t>
+          <t>R5B_STAND</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>13014</v>
+        <v>13004</v>
       </c>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="inlineStr">
@@ -6392,11 +6412,11 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>2167</v>
+        <v>2052</v>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 05</t>
+          <t>B 5번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -6404,16 +6424,16 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_05</t>
+          <t>R5B_SIGN</t>
         </is>
       </c>
       <c r="F79" s="8" t="n">
-        <v>13014</v>
+        <v>13008</v>
       </c>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="inlineStr">
@@ -6424,11 +6444,11 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 06</t>
+          <t>A 5번 방 공식판 01 (진짜 정의)</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -6441,7 +6461,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_06</t>
+          <t>R5A_FORMULA_01</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
@@ -6456,11 +6476,11 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 07</t>
+          <t>A 5번 방 공식판 02</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -6473,7 +6493,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_07</t>
+          <t>R5A_FORMULA_02</t>
         </is>
       </c>
       <c r="F81" s="8" t="n">
@@ -6488,11 +6508,11 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>2170</v>
+        <v>2165</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 08</t>
+          <t>A 5번 방 공식판 03</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -6505,7 +6525,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_08</t>
+          <t>R5A_FORMULA_03</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
@@ -6520,11 +6540,11 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 09</t>
+          <t>A 5번 방 공식판 04</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -6537,7 +6557,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_09</t>
+          <t>R5A_FORMULA_04</t>
         </is>
       </c>
       <c r="F83" s="8" t="n">
@@ -6552,11 +6572,11 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 10</t>
+          <t>A 5번 방 공식판 05</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -6569,7 +6589,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_10</t>
+          <t>R5A_FORMULA_05</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
@@ -6584,11 +6604,11 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>2173</v>
+        <v>2168</v>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 11</t>
+          <t>A 5번 방 공식판 06</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -6601,7 +6621,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_11</t>
+          <t>R5A_FORMULA_06</t>
         </is>
       </c>
       <c r="F85" s="8" t="n">
@@ -6616,11 +6636,11 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 12</t>
+          <t>A 5번 방 공식판 07</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -6633,7 +6653,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_12</t>
+          <t>R5A_FORMULA_07</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
@@ -6648,11 +6668,11 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 13</t>
+          <t>A 5번 방 공식판 08</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -6665,7 +6685,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_13</t>
+          <t>R5A_FORMULA_08</t>
         </is>
       </c>
       <c r="F87" s="8" t="n">
@@ -6680,11 +6700,11 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 14</t>
+          <t>A 5번 방 공식판 09</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -6697,7 +6717,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_14</t>
+          <t>R5A_FORMULA_09</t>
         </is>
       </c>
       <c r="F88" s="8" t="n">
@@ -6712,11 +6732,11 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 15</t>
+          <t>A 5번 방 공식판 10</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -6729,7 +6749,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_15</t>
+          <t>R5A_FORMULA_10</t>
         </is>
       </c>
       <c r="F89" s="8" t="n">
@@ -6744,11 +6764,11 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>2178</v>
+        <v>2173</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 16</t>
+          <t>A 5번 방 공식판 11</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -6761,7 +6781,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_16</t>
+          <t>R5A_FORMULA_11</t>
         </is>
       </c>
       <c r="F90" s="8" t="n">
@@ -6776,11 +6796,11 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>2179</v>
+        <v>2174</v>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 17</t>
+          <t>A 5번 방 공식판 12</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -6793,7 +6813,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_17</t>
+          <t>R5A_FORMULA_12</t>
         </is>
       </c>
       <c r="F91" s="8" t="n">
@@ -6808,11 +6828,11 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 18</t>
+          <t>A 5번 방 공식판 13</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -6825,7 +6845,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_18</t>
+          <t>R5A_FORMULA_13</t>
         </is>
       </c>
       <c r="F92" s="8" t="n">
@@ -6840,11 +6860,11 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>2181</v>
+        <v>2176</v>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 19</t>
+          <t>A 5번 방 공식판 14</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -6857,7 +6877,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_19</t>
+          <t>R5A_FORMULA_14</t>
         </is>
       </c>
       <c r="F93" s="8" t="n">
@@ -6872,11 +6892,11 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 20</t>
+          <t>A 5번 방 공식판 15</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -6889,7 +6909,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_20</t>
+          <t>R5A_FORMULA_15</t>
         </is>
       </c>
       <c r="F94" s="8" t="n">
@@ -6904,15 +6924,15 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>2053</v>
+        <v>2178</v>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 자물쇠 받침대</t>
+          <t>A 5번 방 공식판 16</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
@@ -6921,11 +6941,11 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>R6A_STAND</t>
+          <t>R5A_FORMULA_16</t>
         </is>
       </c>
       <c r="F95" s="8" t="n">
-        <v>13004</v>
+        <v>13014</v>
       </c>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="inlineStr">
@@ -6936,15 +6956,15 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>2055</v>
+        <v>2179</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 글자 표시판</t>
+          <t>A 5번 방 공식판 17</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
@@ -6953,11 +6973,11 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>R6A_SIGN</t>
+          <t>R5A_FORMULA_17</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
-        <v>13008</v>
+        <v>13014</v>
       </c>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="inlineStr">
@@ -6968,28 +6988,28 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>2056</v>
+        <v>2180</v>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 켜진 TV</t>
+          <t>A 5번 방 공식판 18</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N01</t>
+          <t>R5A_FORMULA_18</t>
         </is>
       </c>
       <c r="F97" s="8" t="n">
-        <v>13017</v>
+        <v>13014</v>
       </c>
       <c r="G97" s="8" t="n"/>
       <c r="H97" s="8" t="inlineStr">
@@ -7000,28 +7020,28 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>2057</v>
+        <v>2181</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 켜진 TV</t>
+          <t>A 5번 방 공식판 19</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N02</t>
+          <t>R5A_FORMULA_19</t>
         </is>
       </c>
       <c r="F98" s="8" t="n">
-        <v>13017</v>
+        <v>13014</v>
       </c>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="inlineStr">
@@ -7032,28 +7052,28 @@
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>2058</v>
+        <v>2182</v>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 켜진 TV</t>
+          <t>A 5번 방 공식판 20</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N03</t>
+          <t>R5A_FORMULA_20</t>
         </is>
       </c>
       <c r="F99" s="8" t="n">
-        <v>13017</v>
+        <v>13014</v>
       </c>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="inlineStr">
@@ -7064,11 +7084,11 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>2059</v>
+        <v>2053</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 켜진 TV</t>
+          <t>A 6번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
@@ -7076,16 +7096,16 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N04</t>
+          <t>R6A_STAND</t>
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>13017</v>
+        <v>13004</v>
       </c>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="inlineStr">
@@ -7096,11 +7116,11 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 켜진 TV</t>
+          <t>A 6번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -7108,16 +7128,16 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N05</t>
+          <t>R6A_SIGN</t>
         </is>
       </c>
       <c r="F101" s="8" t="n">
-        <v>13017</v>
+        <v>13008</v>
       </c>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
@@ -7128,7 +7148,7 @@
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
@@ -7145,7 +7165,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N06</t>
+          <t>R6B_TV_N01</t>
         </is>
       </c>
       <c r="F102" s="8" t="n">
@@ -7160,7 +7180,7 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
@@ -7177,7 +7197,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S01</t>
+          <t>R6B_TV_N02</t>
         </is>
       </c>
       <c r="F103" s="8" t="n">
@@ -7192,7 +7212,7 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
@@ -7209,7 +7229,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S02</t>
+          <t>R6B_TV_N03</t>
         </is>
       </c>
       <c r="F104" s="8" t="n">
@@ -7224,7 +7244,7 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
@@ -7241,7 +7261,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S03</t>
+          <t>R6B_TV_N04</t>
         </is>
       </c>
       <c r="F105" s="8" t="n">
@@ -7256,7 +7276,7 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
@@ -7273,7 +7293,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S04</t>
+          <t>R6B_TV_N05</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
@@ -7288,7 +7308,7 @@
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
@@ -7305,7 +7325,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S05</t>
+          <t>R6B_TV_N06</t>
         </is>
       </c>
       <c r="F107" s="8" t="n">
@@ -7320,7 +7340,7 @@
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
@@ -7337,7 +7357,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S06</t>
+          <t>R6B_TV_S01</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
@@ -7352,28 +7372,28 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
-        <v>2070</v>
+        <v>2063</v>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>A 7번 방 자물쇠 받침대</t>
+          <t>B 6번 방 켜진 TV</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>R7A_STAND</t>
+          <t>R6B_TV_S02</t>
         </is>
       </c>
       <c r="F109" s="8" t="n">
-        <v>13004</v>
+        <v>13017</v>
       </c>
       <c r="G109" s="8" t="n"/>
       <c r="H109" s="8" t="inlineStr">
@@ -7384,15 +7404,15 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>2072</v>
+        <v>2064</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>B 7번 방 자물쇠 받침대</t>
+          <t>B 6번 방 켜진 TV</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
@@ -7401,11 +7421,11 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>R7B_STAND</t>
+          <t>R6B_TV_S03</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
-        <v>13004</v>
+        <v>13017</v>
       </c>
       <c r="G110" s="8" t="n"/>
       <c r="H110" s="8" t="inlineStr">
@@ -7416,34 +7436,30 @@
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>2205</v>
+        <v>2065</v>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 1</t>
+          <t>B 6번 방 켜진 TV</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_1</t>
+          <t>R6B_TV_S04</t>
         </is>
       </c>
       <c r="F111" s="8" t="n">
-        <v>13053</v>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
-        </is>
-      </c>
+        <v>13017</v>
+      </c>
+      <c r="G111" s="8" t="n"/>
       <c r="H111" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7452,34 +7468,30 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>2206</v>
+        <v>2066</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 2</t>
+          <t>B 6번 방 켜진 TV</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_2</t>
+          <t>R6B_TV_S05</t>
         </is>
       </c>
       <c r="F112" s="8" t="n">
-        <v>13053</v>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
-        </is>
-      </c>
+        <v>13017</v>
+      </c>
+      <c r="G112" s="8" t="n"/>
       <c r="H112" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7488,34 +7500,30 @@
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
-        <v>2207</v>
+        <v>2067</v>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 3</t>
+          <t>B 6번 방 켜진 TV</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_3</t>
+          <t>R6B_TV_S06</t>
         </is>
       </c>
       <c r="F113" s="8" t="n">
-        <v>13053</v>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
-        </is>
-      </c>
+        <v>13017</v>
+      </c>
+      <c r="G113" s="8" t="n"/>
       <c r="H113" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7524,15 +7532,15 @@
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>2208</v>
+        <v>2070</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 4</t>
+          <t>A 7번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
@@ -7541,17 +7549,13 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_4</t>
+          <t>R7A_STAND</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
-        <v>13053</v>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
-        </is>
-      </c>
+        <v>13004</v>
+      </c>
+      <c r="G114" s="8" t="n"/>
       <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7560,34 +7564,30 @@
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
-        <v>2209</v>
+        <v>2072</v>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 5</t>
+          <t>B 7번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_5</t>
+          <t>R7B_STAND</t>
         </is>
       </c>
       <c r="F115" s="8" t="n">
-        <v>13053</v>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
-        </is>
-      </c>
+        <v>13004</v>
+      </c>
+      <c r="G115" s="8" t="n"/>
       <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7596,11 +7596,11 @@
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 6</t>
+          <t>A 2번 방 큰 풀 1</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_6</t>
+          <t>R02_A_BigGrassPoint_1</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
@@ -7632,11 +7632,11 @@
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
-        <v>2211</v>
+        <v>2206</v>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 1</t>
+          <t>A 2번 방 큰 풀 2</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
@@ -7649,15 +7649,15 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_1</t>
+          <t>R02_A_BigGrassPoint_2</t>
         </is>
       </c>
       <c r="F117" s="8" t="n">
-        <v>13050</v>
+        <v>13053</v>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
@@ -7668,11 +7668,11 @@
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 2</t>
+          <t>A 2번 방 큰 풀 3</t>
         </is>
       </c>
       <c r="C118" s="8" t="n">
@@ -7685,15 +7685,15 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_2</t>
+          <t>R02_A_BigGrassPoint_3</t>
         </is>
       </c>
       <c r="F118" s="8" t="n">
-        <v>13050</v>
+        <v>13053</v>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
@@ -7704,11 +7704,11 @@
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
-        <v>2213</v>
+        <v>2208</v>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 3</t>
+          <t>A 2번 방 큰 풀 4</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
@@ -7721,15 +7721,15 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_3</t>
+          <t>R02_A_BigGrassPoint_4</t>
         </is>
       </c>
       <c r="F119" s="8" t="n">
-        <v>13050</v>
+        <v>13053</v>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -7740,11 +7740,11 @@
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>2214</v>
+        <v>2209</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 4</t>
+          <t>A 2번 방 큰 풀 5</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
@@ -7757,15 +7757,15 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_4</t>
+          <t>R02_A_BigGrassPoint_5</t>
         </is>
       </c>
       <c r="F120" s="8" t="n">
-        <v>13050</v>
+        <v>13053</v>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
@@ -7776,11 +7776,11 @@
     </row>
     <row r="121">
       <c r="A121" s="8" t="n">
-        <v>2215</v>
+        <v>2210</v>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 1</t>
+          <t>A 2번 방 큰 풀 6</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -7793,15 +7793,15 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_1</t>
+          <t>R02_A_BigGrassPoint_6</t>
         </is>
       </c>
       <c r="F121" s="8" t="n">
-        <v>13051</v>
+        <v>13053</v>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
@@ -7812,11 +7812,11 @@
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>2216</v>
+        <v>2211</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 2</t>
+          <t>A 2번 방 의자 1</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -7829,11 +7829,11 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_2</t>
+          <t>R02_A_ChairPoint_1</t>
         </is>
       </c>
       <c r="F122" s="8" t="n">
-        <v>13051</v>
+        <v>13050</v>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
@@ -7848,11 +7848,11 @@
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 3</t>
+          <t>A 2번 방 의자 2</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
@@ -7865,11 +7865,11 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_3</t>
+          <t>R02_A_ChairPoint_2</t>
         </is>
       </c>
       <c r="F123" s="8" t="n">
-        <v>13051</v>
+        <v>13050</v>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
@@ -7884,11 +7884,11 @@
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>2218</v>
+        <v>2213</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 4</t>
+          <t>A 2번 방 의자 3</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
@@ -7901,11 +7901,11 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_4</t>
+          <t>R02_A_ChairPoint_3</t>
         </is>
       </c>
       <c r="F124" s="8" t="n">
-        <v>13051</v>
+        <v>13050</v>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
@@ -7920,11 +7920,11 @@
     </row>
     <row r="125">
       <c r="A125" s="8" t="n">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 5</t>
+          <t>A 2번 방 의자 4</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
@@ -7937,11 +7937,11 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_5</t>
+          <t>R02_A_ChairPoint_4</t>
         </is>
       </c>
       <c r="F125" s="8" t="n">
-        <v>13051</v>
+        <v>13050</v>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
@@ -7956,11 +7956,11 @@
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>2220</v>
+        <v>2215</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 6</t>
+          <t>A 2번 방 조명 1</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_6</t>
+          <t>R02_A_LightPoint_1</t>
         </is>
       </c>
       <c r="F126" s="8" t="n">
@@ -7992,11 +7992,11 @@
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>2221</v>
+        <v>2216</v>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 7</t>
+          <t>A 2번 방 조명 2</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_7</t>
+          <t>R02_A_LightPoint_2</t>
         </is>
       </c>
       <c r="F127" s="8" t="n">
@@ -8028,11 +8028,11 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>2222</v>
+        <v>2217</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 8</t>
+          <t>A 2번 방 조명 3</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_8</t>
+          <t>R02_A_LightPoint_3</t>
         </is>
       </c>
       <c r="F128" s="8" t="n">
@@ -8064,11 +8064,11 @@
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
-        <v>2223</v>
+        <v>2218</v>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 1</t>
+          <t>A 2번 방 조명 4</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
@@ -8076,16 +8076,16 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_1</t>
+          <t>R02_A_LightPoint_4</t>
         </is>
       </c>
       <c r="F129" s="8" t="n">
-        <v>13053</v>
+        <v>13051</v>
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
@@ -8100,11 +8100,11 @@
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
-        <v>2224</v>
+        <v>2219</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 2</t>
+          <t>A 2번 방 조명 5</t>
         </is>
       </c>
       <c r="C130" s="8" t="n">
@@ -8112,16 +8112,16 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_2</t>
+          <t>R02_A_LightPoint_5</t>
         </is>
       </c>
       <c r="F130" s="8" t="n">
-        <v>13053</v>
+        <v>13051</v>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
@@ -8136,11 +8136,11 @@
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 3</t>
+          <t>A 2번 방 조명 6</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
@@ -8148,16 +8148,16 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_3</t>
+          <t>R02_A_LightPoint_6</t>
         </is>
       </c>
       <c r="F131" s="8" t="n">
-        <v>13053</v>
+        <v>13051</v>
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
@@ -8172,11 +8172,11 @@
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 4</t>
+          <t>A 2번 방 조명 7</t>
         </is>
       </c>
       <c r="C132" s="8" t="n">
@@ -8184,16 +8184,16 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_4</t>
+          <t>R02_A_LightPoint_7</t>
         </is>
       </c>
       <c r="F132" s="8" t="n">
-        <v>13053</v>
+        <v>13051</v>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
@@ -8208,11 +8208,11 @@
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
-        <v>2227</v>
+        <v>2222</v>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 5</t>
+          <t>A 2번 방 조명 8</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
@@ -8220,16 +8220,16 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_5</t>
+          <t>R02_A_LightPoint_8</t>
         </is>
       </c>
       <c r="F133" s="8" t="n">
-        <v>13053</v>
+        <v>13051</v>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
@@ -8244,11 +8244,11 @@
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 6</t>
+          <t>B 2번 방 큰 풀 1</t>
         </is>
       </c>
       <c r="C134" s="8" t="n">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_6</t>
+          <t>R02_BigGrassPoint_1</t>
         </is>
       </c>
       <c r="F134" s="8" t="n">
@@ -8280,11 +8280,11 @@
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
-        <v>2229</v>
+        <v>2224</v>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 7</t>
+          <t>B 2번 방 큰 풀 2</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_7</t>
+          <t>R02_BigGrassPoint_2</t>
         </is>
       </c>
       <c r="F135" s="8" t="n">
@@ -8316,11 +8316,11 @@
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>2230</v>
+        <v>2225</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 9</t>
+          <t>B 2번 방 큰 풀 3</t>
         </is>
       </c>
       <c r="C136" s="8" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_9</t>
+          <t>R02_BigGrassPoint_3</t>
         </is>
       </c>
       <c r="F136" s="8" t="n">
@@ -8352,11 +8352,11 @@
     </row>
     <row r="137">
       <c r="A137" s="8" t="n">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 10</t>
+          <t>B 2번 방 큰 풀 4</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_10</t>
+          <t>R02_BigGrassPoint_4</t>
         </is>
       </c>
       <c r="F137" s="8" t="n">
@@ -8388,11 +8388,11 @@
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>2232</v>
+        <v>2227</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 11</t>
+          <t>B 2번 방 큰 풀 5</t>
         </is>
       </c>
       <c r="C138" s="8" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_11</t>
+          <t>R02_BigGrassPoint_5</t>
         </is>
       </c>
       <c r="F138" s="8" t="n">
@@ -8424,11 +8424,11 @@
     </row>
     <row r="139">
       <c r="A139" s="8" t="n">
-        <v>2233</v>
+        <v>2228</v>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 작은 풀 1</t>
+          <t>B 2번 방 큰 풀 6</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
@@ -8441,11 +8441,11 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>R02_SmallGrassPoint_1</t>
+          <t>R02_BigGrassPoint_6</t>
         </is>
       </c>
       <c r="F139" s="8" t="n">
-        <v>13054</v>
+        <v>13053</v>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
@@ -8460,11 +8460,11 @@
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 작은 풀 2</t>
+          <t>B 2번 방 큰 풀 7</t>
         </is>
       </c>
       <c r="C140" s="8" t="n">
@@ -8477,18 +8477,198 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
+          <t>R02_BigGrassPoint_7</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>13053</v>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>장식</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="n">
+        <v>2230</v>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>B 2번 방 큰 풀 9</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>R02_BigGrassPoint_9</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="n">
+        <v>13053</v>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>장식</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n">
+        <v>2231</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>B 2번 방 큰 풀 10</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>R02_BigGrassPoint_10</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>13053</v>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>장식</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="n">
+        <v>2232</v>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>B 2번 방 큰 풀 11</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>R02_BigGrassPoint_11</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>13053</v>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>장식</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n">
+        <v>2233</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>B 2번 방 작은 풀 1</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>R02_SmallGrassPoint_1</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="n">
+        <v>13054</v>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>장식</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="n">
+        <v>2234</v>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>B 2번 방 작은 풀 2</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
           <t>R02_SmallGrassPoint_2</t>
         </is>
       </c>
-      <c r="F140" s="8" t="n">
+      <c r="F145" s="8" t="n">
         <v>13054</v>
       </c>
-      <c r="G140" s="8" t="inlineStr">
+      <c r="G145" s="8" t="inlineStr">
         <is>
           <t>장식</t>
         </is>
       </c>
-      <c r="H140" s="8" t="inlineStr">
+      <c r="H145" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -3735,7 +3735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>A 1번 방 시작 위치</t>
+          <t>1번 방 시작 위치 (A·B 공통)</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>R01A_Player</t>
+          <t>R01_Player</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 R01A_Player (사용자가 직접 배치, 2026-10-20). 프리팹 13001 경로는 아직 예시라 실제 플레이어 시작 프리팹이 필요함</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 R01_Player (A · B가 같은 자리에서 시작, 사용자 결정). 프리팹 13001 경로는 아직 예시라 실제 플레이어 시작 프리팹이 필요함</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -4212,11 +4212,11 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>2003</v>
+        <v>2237</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>B 1번 방 시작 위치</t>
+          <t>A 1번 방 바닥 카드</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -4224,20 +4224,20 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>R01B_Player</t>
+          <t>R01A_CardsPoint</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>13001</v>
+        <v>13067</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01B 아래 R01B_Player (사용자가 직접 배치, 2026-10-20). 프리팹 13001 경로는 아직 예시라 실제 플레이어 시작 프리팹이 필요함</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -4248,11 +4248,11 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A 1번 방 바닥 카드</t>
+          <t>1번 방 천장 (A·B 공통)</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -4260,20 +4260,20 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>R01A_CardsPoint</t>
+          <t>R01_CeilingPoint</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>13067</v>
+        <v>13068</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -4284,11 +4284,11 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>1번 방 천장 (A·B 공통)</t>
+          <t>1번 방 바닥·벽 (A·B 공통)</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -4301,30 +4301,30 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>R01_CeilingPoint</t>
+          <t>R01_StructurePoint</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>13068</v>
+        <v>13069</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
+          <t>바닥·벽은 방 프리팹(Room_01_Final, PREFAB 13020/13027) 자체라 따로 스폰하지 않음. 앵커 오브젝트는 프리팹 안에 남아 있음</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>1번 방 바닥·벽 (A·B 공통)</t>
+          <t>1번 방 문 막기용 문 dver' (A·B 공통)</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
@@ -4337,30 +4337,30 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>R01_StructurePoint</t>
+          <t>R01_DverPoint</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>13069</v>
+        <v>13070</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>바닥·벽은 방 프리팹(Room_01_Final, PREFAB 13020/13027) 자체라 따로 스폰하지 않음. 앵커 오브젝트는 프리팹 안에 남아 있음</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>1번 방 문 막기용 문 dver' (A·B 공통)</t>
+          <t>1번 방 서랍장 (A·B 공통)</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -4373,15 +4373,15 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>R01_DverPoint</t>
+          <t>R01_DrawerPoint</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>13070</v>
+        <v>13071</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -4392,34 +4392,30 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2241</v>
+        <v>2033</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>1번 방 서랍장 (A·B 공통)</t>
+          <t>A 2번 방 테이블</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>R01_DrawerPoint</t>
+          <t>R02_A_TablePoint</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>13071</v>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
-        </is>
-      </c>
+        <v>13052</v>
+      </c>
+      <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4428,11 +4424,11 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 테이블</t>
+          <t>A 2번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -4445,11 +4441,11 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>R02_A_TablePoint</t>
+          <t>R2A_SIGN</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>13052</v>
+        <v>13008</v>
       </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="inlineStr">
@@ -4460,11 +4456,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2035</v>
+        <v>2125</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 글자 표시판</t>
+          <t>B 2번 방 액자 01</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -4472,18 +4468,22 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>R2A_SIGN</t>
+          <t>R02_RedFramePoint_1</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G24" s="8" t="n"/>
+        <v>13063</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>색 Red</t>
+        </is>
+      </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4492,11 +4492,11 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 01</t>
+          <t>B 2번 방 액자 02</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>R02_RedFramePoint_1</t>
+          <t>R02_RedFramePoint_2</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
@@ -4528,11 +4528,11 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 02</t>
+          <t>B 2번 방 액자 03</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -4545,15 +4545,15 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>R02_RedFramePoint_2</t>
+          <t>R02_BlueFramePoint_2</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13063</v>
+        <v>13056</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>색 Red</t>
+          <t>색 Blue</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -4564,11 +4564,11 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 03</t>
+          <t>B 2번 방 액자 04</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -4581,15 +4581,15 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>R02_BlueFramePoint_2</t>
+          <t>R02_YellowFramePoint_4</t>
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>13056</v>
+        <v>13064</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>색 Blue</t>
+          <t>색 Yellow</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -4600,11 +4600,11 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 04</t>
+          <t>B 2번 방 액자 05</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -4617,15 +4617,15 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_4</t>
+          <t>R02_GreenFramePoint_1</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>13064</v>
+        <v>13058</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>색 Green</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -4636,11 +4636,11 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 05</t>
+          <t>B 2번 방 액자 06</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_1</t>
+          <t>R02_GreenFramePoint_2</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>색 Green</t>
+          <t>색 Green. Unity 이름에 공백('R02_GreenFramePoint _2'), 표에는 공백 없이 씀</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -4672,11 +4672,11 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 06</t>
+          <t>B 2번 방 액자 07</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_2</t>
+          <t>R02_GreenFramePoint_3</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>색 Green. Unity 이름에 공백('R02_GreenFramePoint _2'), 표에는 공백 없이 씀</t>
+          <t>색 Green</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -4708,11 +4708,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 07</t>
+          <t>B 2번 방 액자 08</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_3</t>
+          <t>R02_GreenFramePoint_4</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
@@ -4744,11 +4744,11 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 08</t>
+          <t>B 2번 방 액자 09</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -4761,15 +4761,15 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_4</t>
+          <t>R02_BlackFramePoint_2</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>13058</v>
+        <v>13055</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>색 Green</t>
+          <t>색 Black</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -4780,11 +4780,11 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 09</t>
+          <t>B 2번 방 액자 10</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -4797,15 +4797,15 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>R02_BlackFramePoint_2</t>
+          <t>R02_PuppleFreamPoint_3</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>13055</v>
+        <v>13062</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>색 Black</t>
+          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -4816,11 +4816,11 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 10</t>
+          <t>B 2번 방 액자 11</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_3</t>
+          <t>R02_PuppleFreamPoint_4</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
@@ -4852,11 +4852,11 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 11</t>
+          <t>B 2번 방 액자 12</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -4869,15 +4869,15 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_4</t>
+          <t>R02_NavyFreamPoint_2</t>
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>13062</v>
+        <v>13060</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>색 Navy</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -4888,11 +4888,11 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 12</t>
+          <t>B 2번 방 액자 13</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_2</t>
+          <t>R02_NavyFreamPoint_3</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
@@ -4924,11 +4924,11 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 13</t>
+          <t>B 2번 방 액자 14</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -4941,15 +4941,15 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_3</t>
+          <t>R02_BlueFramePoint_1</t>
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>13060</v>
+        <v>13056</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>색 Navy</t>
+          <t>색 Blue</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -4960,11 +4960,11 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 14</t>
+          <t>B 2번 방 액자 15</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -4977,15 +4977,15 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>R02_BlueFramePoint_1</t>
+          <t>R02_GrayFramePoint_1</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>13056</v>
+        <v>13057</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>색 Blue</t>
+          <t>색 Gray</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -4996,11 +4996,11 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 15</t>
+          <t>B 2번 방 액자 16</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>R02_GrayFramePoint_1</t>
+          <t>R02_GrayFramePoint_2</t>
         </is>
       </c>
       <c r="F39" s="8" t="n">
@@ -5032,11 +5032,11 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 16</t>
+          <t>B 2번 방 액자 17</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -5049,15 +5049,15 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>R02_GrayFramePoint_2</t>
+          <t>R02_YellowFramePoint_1</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>13057</v>
+        <v>13064</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>색 Gray</t>
+          <t>색 Yellow</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -5068,11 +5068,11 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 17</t>
+          <t>B 2번 방 액자 18</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_1</t>
+          <t>R02_YellowFramePoint_2</t>
         </is>
       </c>
       <c r="F41" s="8" t="n">
@@ -5104,11 +5104,11 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 18</t>
+          <t>B 2번 방 액자 19</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_2</t>
+          <t>R02_YellowFramePoint_3</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
@@ -5140,11 +5140,11 @@
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 19</t>
+          <t>B 2번 방 액자 20</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -5157,15 +5157,15 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_3</t>
+          <t>R02_OrangeFreamPoint_1</t>
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>13064</v>
+        <v>13061</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>색 Orange</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -5176,11 +5176,11 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 20</t>
+          <t>B 2번 방 액자 21</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>R02_OrangeFreamPoint_1</t>
+          <t>R02_OrangeFreamPoint_2</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
@@ -5212,11 +5212,11 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 21</t>
+          <t>B 2번 방 액자 22</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -5229,15 +5229,15 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>R02_OrangeFreamPoint_2</t>
+          <t>R02_BlackFramePoint_1</t>
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>13061</v>
+        <v>13055</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>색 Orange</t>
+          <t>색 Black</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -5248,11 +5248,11 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 22</t>
+          <t>B 2번 방 액자 23</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -5265,15 +5265,15 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>R02_BlackFramePoint_1</t>
+          <t>R02_PuppleFreamPoint_1</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>13055</v>
+        <v>13062</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>색 Black</t>
+          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -5284,11 +5284,11 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 23</t>
+          <t>B 2번 방 액자 24</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_1</t>
+          <t>R02_PuppleFreamPoint_2</t>
         </is>
       </c>
       <c r="F47" s="8" t="n">
@@ -5320,11 +5320,11 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 24</t>
+          <t>B 2번 방 액자 25</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -5337,15 +5337,15 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_2</t>
+          <t>R02_MintFramePoint_1</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>13062</v>
+        <v>13059</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -5356,11 +5356,11 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 25</t>
+          <t>B 2번 방 액자 26</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>R02_MintFramePoint_1</t>
+          <t>R02_MintFramePoint_2</t>
         </is>
       </c>
       <c r="F49" s="8" t="n">
@@ -5392,11 +5392,11 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 26</t>
+          <t>B 2번 방 액자 28</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -5409,15 +5409,15 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>R02_MintFramePoint_2</t>
+          <t>R02_NavyFreamPoint_1</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>13059</v>
+        <v>13060</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
+          <t>색 Navy</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -5428,15 +5428,15 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>2152</v>
+        <v>2040</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 28</t>
+          <t>B 3번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
@@ -5445,17 +5445,13 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_1</t>
+          <t>R3B_SIGN</t>
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>13060</v>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>색 Navy</t>
-        </is>
-      </c>
+        <v>13008</v>
+      </c>
+      <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5464,11 +5460,11 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>2040</v>
+        <v>2183</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 글자 표시판</t>
+          <t>A 3번 방 단서 화살표 01</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -5476,18 +5472,22 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>R3B_SIGN</t>
+          <t>R3A_ARROW_01</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G52" s="8" t="n"/>
+        <v>13011</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
+        </is>
+      </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5496,11 +5496,11 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 01</t>
+          <t>A 3번 방 단서 화살표 02</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_01</t>
+          <t>R3A_ARROW_02</t>
         </is>
       </c>
       <c r="F53" s="8" t="n">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -5532,11 +5532,11 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 02</t>
+          <t>A 3번 방 단서 화살표 03</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_02</t>
+          <t>R3A_ARROW_03</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -5568,11 +5568,11 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 03</t>
+          <t>A 3번 방 단서 화살표 04</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_03</t>
+          <t>R3A_ARROW_04</t>
         </is>
       </c>
       <c r="F55" s="8" t="n">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -5604,11 +5604,11 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 04</t>
+          <t>A 3번 방 단서 화살표 05</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_04</t>
+          <t>R3A_ARROW_05</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -5640,11 +5640,11 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 05</t>
+          <t>A 3번 방 단서 화살표 06</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_05</t>
+          <t>R3A_ARROW_06</t>
         </is>
       </c>
       <c r="F57" s="8" t="n">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -5676,11 +5676,11 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 06</t>
+          <t>A 3번 방 단서 화살표 07</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_06</t>
+          <t>R3A_ARROW_07</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -5712,11 +5712,11 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 07</t>
+          <t>A 3번 방 단서 화살표 08</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_07</t>
+          <t>R3A_ARROW_08</t>
         </is>
       </c>
       <c r="F59" s="8" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -5748,11 +5748,11 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 08</t>
+          <t>A 3번 방 단서 화살표 09</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_08</t>
+          <t>R3A_ARROW_09</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -5784,11 +5784,11 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 09</t>
+          <t>A 3번 방 단서 화살표 10</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_09</t>
+          <t>R3A_ARROW_10</t>
         </is>
       </c>
       <c r="F61" s="8" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -5820,15 +5820,15 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>2192</v>
+        <v>2041</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 10</t>
+          <t>A 4번 방 테이블</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
@@ -5837,17 +5837,13 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_10</t>
+          <t>R4A_TABLE</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>13011</v>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
-        </is>
-      </c>
+        <v>13003</v>
+      </c>
+      <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5856,11 +5852,11 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 테이블</t>
+          <t>A 4번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -5873,11 +5869,11 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>R4A_TABLE</t>
+          <t>R4A_SIGN</t>
         </is>
       </c>
       <c r="F63" s="8" t="n">
-        <v>13003</v>
+        <v>13008</v>
       </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="inlineStr">
@@ -5888,11 +5884,11 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>2043</v>
+        <v>2074</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 글자 표시판</t>
+          <t>B 4번 방 배선 콘솔 받침대</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -5900,18 +5896,22 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>R4A_SIGN</t>
+          <t>R4B_CONSOLE_STAND</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G64" s="8" t="n"/>
+        <v>13019</v>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
+        </is>
+      </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5920,11 +5920,11 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>2074</v>
+        <v>2153</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 배선 콘솔 받침대</t>
+          <t>B 4번 방 전선 01 (정답)</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -5937,15 +5937,15 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>R4B_CONSOLE_STAND</t>
+          <t>R4B_WIRE_01</t>
         </is>
       </c>
       <c r="F65" s="8" t="n">
-        <v>13019</v>
+        <v>13034</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
+          <t>배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -5956,11 +5956,11 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 01 (정답)</t>
+          <t>B 4번 방 전선 02 (정답)</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_01</t>
+          <t>R4B_WIRE_02</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
@@ -5992,11 +5992,11 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 02 (정답)</t>
+          <t>B 4번 방 전선 03 (정답)</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_02</t>
+          <t>R4B_WIRE_03</t>
         </is>
       </c>
       <c r="F67" s="8" t="n">
@@ -6028,11 +6028,11 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 03 (정답)</t>
+          <t>B 4번 방 전선 04 (정답)</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_03</t>
+          <t>R4B_WIRE_04</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
@@ -6064,11 +6064,11 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 04 (정답)</t>
+          <t>B 4번 방 전선 05 (정답)</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_04</t>
+          <t>R4B_WIRE_05</t>
         </is>
       </c>
       <c r="F69" s="8" t="n">
@@ -6100,11 +6100,11 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 05 (정답)</t>
+          <t>B 4번 방 전선 06 (가짜)</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_05</t>
+          <t>R4B_WIRE_06</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
@@ -6136,11 +6136,11 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 06 (가짜)</t>
+          <t>B 4번 방 전선 07 (가짜)</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_06</t>
+          <t>R4B_WIRE_07</t>
         </is>
       </c>
       <c r="F71" s="8" t="n">
@@ -6172,11 +6172,11 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 07 (가짜)</t>
+          <t>B 4번 방 전선 08 (가짜)</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_07</t>
+          <t>R4B_WIRE_08</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
@@ -6208,11 +6208,11 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 08 (가짜)</t>
+          <t>B 4번 방 전선 09 (가짜)</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_08</t>
+          <t>R4B_WIRE_09</t>
         </is>
       </c>
       <c r="F73" s="8" t="n">
@@ -6244,11 +6244,11 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 09 (가짜)</t>
+          <t>B 4번 방 전선 10 (가짜)</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_09</t>
+          <t>R4B_WIRE_10</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
@@ -6280,34 +6280,30 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>2162</v>
+        <v>2048</v>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 10 (가짜)</t>
+          <t>A 5번 방 테이블</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_10</t>
+          <t>R5A_TABLE</t>
         </is>
       </c>
       <c r="F75" s="8" t="n">
-        <v>13034</v>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>배선 콘솔 안 단자에 연결</t>
-        </is>
-      </c>
+        <v>13003</v>
+      </c>
+      <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6316,11 +6312,11 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 테이블</t>
+          <t>A 5번 방 종이</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
@@ -6333,11 +6329,11 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>R5A_TABLE</t>
+          <t>R5A_PAPER</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>13003</v>
+        <v>13016</v>
       </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="inlineStr">
@@ -6348,11 +6344,11 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 종이</t>
+          <t>B 5번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -6360,16 +6356,16 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>R5A_PAPER</t>
+          <t>R5B_STAND</t>
         </is>
       </c>
       <c r="F77" s="8" t="n">
-        <v>13016</v>
+        <v>13004</v>
       </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
@@ -6380,11 +6376,11 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 자물쇠 받침대</t>
+          <t>B 5번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -6397,11 +6393,11 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>R5B_STAND</t>
+          <t>R5B_SIGN</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>13004</v>
+        <v>13008</v>
       </c>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="inlineStr">
@@ -6412,11 +6408,11 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>2052</v>
+        <v>2163</v>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 글자 표시판</t>
+          <t>A 5번 방 공식판 01 (진짜 정의)</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -6424,16 +6420,16 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>R5B_SIGN</t>
+          <t>R5A_FORMULA_01</t>
         </is>
       </c>
       <c r="F79" s="8" t="n">
-        <v>13008</v>
+        <v>13014</v>
       </c>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="inlineStr">
@@ -6444,11 +6440,11 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 01 (진짜 정의)</t>
+          <t>A 5번 방 공식판 02</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -6461,7 +6457,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_01</t>
+          <t>R5A_FORMULA_02</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
@@ -6476,11 +6472,11 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 02</t>
+          <t>A 5번 방 공식판 03</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -6493,7 +6489,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_02</t>
+          <t>R5A_FORMULA_03</t>
         </is>
       </c>
       <c r="F81" s="8" t="n">
@@ -6508,11 +6504,11 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 03</t>
+          <t>A 5번 방 공식판 04</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -6525,7 +6521,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_03</t>
+          <t>R5A_FORMULA_04</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
@@ -6540,11 +6536,11 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 04</t>
+          <t>A 5번 방 공식판 05</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -6557,7 +6553,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_04</t>
+          <t>R5A_FORMULA_05</t>
         </is>
       </c>
       <c r="F83" s="8" t="n">
@@ -6572,11 +6568,11 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 05</t>
+          <t>A 5번 방 공식판 06</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -6589,7 +6585,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_05</t>
+          <t>R5A_FORMULA_06</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
@@ -6604,11 +6600,11 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 06</t>
+          <t>A 5번 방 공식판 07</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -6621,7 +6617,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_06</t>
+          <t>R5A_FORMULA_07</t>
         </is>
       </c>
       <c r="F85" s="8" t="n">
@@ -6636,11 +6632,11 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 07</t>
+          <t>A 5번 방 공식판 08</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -6653,7 +6649,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_07</t>
+          <t>R5A_FORMULA_08</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
@@ -6668,11 +6664,11 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 08</t>
+          <t>A 5번 방 공식판 09</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -6685,7 +6681,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_08</t>
+          <t>R5A_FORMULA_09</t>
         </is>
       </c>
       <c r="F87" s="8" t="n">
@@ -6700,11 +6696,11 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 09</t>
+          <t>A 5번 방 공식판 10</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -6717,7 +6713,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_09</t>
+          <t>R5A_FORMULA_10</t>
         </is>
       </c>
       <c r="F88" s="8" t="n">
@@ -6732,11 +6728,11 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 10</t>
+          <t>A 5번 방 공식판 11</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -6749,7 +6745,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_10</t>
+          <t>R5A_FORMULA_11</t>
         </is>
       </c>
       <c r="F89" s="8" t="n">
@@ -6764,11 +6760,11 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 11</t>
+          <t>A 5번 방 공식판 12</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -6781,7 +6777,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_11</t>
+          <t>R5A_FORMULA_12</t>
         </is>
       </c>
       <c r="F90" s="8" t="n">
@@ -6796,11 +6792,11 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 12</t>
+          <t>A 5번 방 공식판 13</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -6813,7 +6809,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_12</t>
+          <t>R5A_FORMULA_13</t>
         </is>
       </c>
       <c r="F91" s="8" t="n">
@@ -6828,11 +6824,11 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 13</t>
+          <t>A 5번 방 공식판 14</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -6845,7 +6841,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_13</t>
+          <t>R5A_FORMULA_14</t>
         </is>
       </c>
       <c r="F92" s="8" t="n">
@@ -6860,11 +6856,11 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 14</t>
+          <t>A 5번 방 공식판 15</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -6877,7 +6873,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_14</t>
+          <t>R5A_FORMULA_15</t>
         </is>
       </c>
       <c r="F93" s="8" t="n">
@@ -6892,11 +6888,11 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 15</t>
+          <t>A 5번 방 공식판 16</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -6909,7 +6905,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_15</t>
+          <t>R5A_FORMULA_16</t>
         </is>
       </c>
       <c r="F94" s="8" t="n">
@@ -6924,11 +6920,11 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 16</t>
+          <t>A 5번 방 공식판 17</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -6941,7 +6937,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_16</t>
+          <t>R5A_FORMULA_17</t>
         </is>
       </c>
       <c r="F95" s="8" t="n">
@@ -6956,11 +6952,11 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 17</t>
+          <t>A 5번 방 공식판 18</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -6973,7 +6969,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_17</t>
+          <t>R5A_FORMULA_18</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
@@ -6988,11 +6984,11 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 18</t>
+          <t>A 5번 방 공식판 19</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -7005,7 +7001,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_18</t>
+          <t>R5A_FORMULA_19</t>
         </is>
       </c>
       <c r="F97" s="8" t="n">
@@ -7020,11 +7016,11 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 19</t>
+          <t>A 5번 방 공식판 20</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -7037,7 +7033,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_19</t>
+          <t>R5A_FORMULA_20</t>
         </is>
       </c>
       <c r="F98" s="8" t="n">
@@ -7052,15 +7048,15 @@
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>2182</v>
+        <v>2053</v>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 20</t>
+          <t>A 6번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
@@ -7069,11 +7065,11 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_20</t>
+          <t>R6A_STAND</t>
         </is>
       </c>
       <c r="F99" s="8" t="n">
-        <v>13014</v>
+        <v>13004</v>
       </c>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="inlineStr">
@@ -7084,11 +7080,11 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 자물쇠 받침대</t>
+          <t>A 6번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
@@ -7101,11 +7097,11 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>R6A_STAND</t>
+          <t>R6A_SIGN</t>
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>13004</v>
+        <v>13008</v>
       </c>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="inlineStr">
@@ -7116,11 +7112,11 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 글자 표시판</t>
+          <t>B 6번 방 켜진 TV</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -7128,16 +7124,16 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>R6A_SIGN</t>
+          <t>R6B_TV_N01</t>
         </is>
       </c>
       <c r="F101" s="8" t="n">
-        <v>13008</v>
+        <v>13017</v>
       </c>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
@@ -7148,7 +7144,7 @@
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
@@ -7165,7 +7161,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N01</t>
+          <t>R6B_TV_N02</t>
         </is>
       </c>
       <c r="F102" s="8" t="n">
@@ -7180,7 +7176,7 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
@@ -7197,7 +7193,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N02</t>
+          <t>R6B_TV_N03</t>
         </is>
       </c>
       <c r="F103" s="8" t="n">
@@ -7212,7 +7208,7 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
@@ -7229,7 +7225,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N03</t>
+          <t>R6B_TV_N04</t>
         </is>
       </c>
       <c r="F104" s="8" t="n">
@@ -7244,7 +7240,7 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
@@ -7261,7 +7257,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N04</t>
+          <t>R6B_TV_N05</t>
         </is>
       </c>
       <c r="F105" s="8" t="n">
@@ -7276,7 +7272,7 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
@@ -7293,7 +7289,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N05</t>
+          <t>R6B_TV_N06</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
@@ -7308,7 +7304,7 @@
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
@@ -7325,7 +7321,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N06</t>
+          <t>R6B_TV_S01</t>
         </is>
       </c>
       <c r="F107" s="8" t="n">
@@ -7340,7 +7336,7 @@
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
@@ -7357,7 +7353,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S01</t>
+          <t>R6B_TV_S02</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
@@ -7372,7 +7368,7 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
@@ -7389,7 +7385,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S02</t>
+          <t>R6B_TV_S03</t>
         </is>
       </c>
       <c r="F109" s="8" t="n">
@@ -7404,7 +7400,7 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
@@ -7421,7 +7417,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S03</t>
+          <t>R6B_TV_S04</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
@@ -7436,7 +7432,7 @@
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
@@ -7453,7 +7449,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S04</t>
+          <t>R6B_TV_S05</t>
         </is>
       </c>
       <c r="F111" s="8" t="n">
@@ -7468,7 +7464,7 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
@@ -7485,7 +7481,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S05</t>
+          <t>R6B_TV_S06</t>
         </is>
       </c>
       <c r="F112" s="8" t="n">
@@ -7500,28 +7496,28 @@
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 켜진 TV</t>
+          <t>A 7번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S06</t>
+          <t>R7A_STAND</t>
         </is>
       </c>
       <c r="F113" s="8" t="n">
-        <v>13017</v>
+        <v>13004</v>
       </c>
       <c r="G113" s="8" t="n"/>
       <c r="H113" s="8" t="inlineStr">
@@ -7532,11 +7528,11 @@
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>A 7번 방 자물쇠 받침대</t>
+          <t>B 7번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
@@ -7544,12 +7540,12 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>R7A_STAND</t>
+          <t>R7B_STAND</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
@@ -7564,30 +7560,34 @@
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
-        <v>2072</v>
+        <v>2205</v>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>B 7번 방 자물쇠 받침대</t>
+          <t>A 2번 방 큰 풀 1</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>R7B_STAND</t>
+          <t>R02_A_BigGrassPoint_1</t>
         </is>
       </c>
       <c r="F115" s="8" t="n">
-        <v>13004</v>
-      </c>
-      <c r="G115" s="8" t="n"/>
+        <v>13053</v>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
+        </is>
+      </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7596,11 +7596,11 @@
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 1</t>
+          <t>A 2번 방 큰 풀 2</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_1</t>
+          <t>R02_A_BigGrassPoint_2</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
@@ -7632,11 +7632,11 @@
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 2</t>
+          <t>A 2번 방 큰 풀 3</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_2</t>
+          <t>R02_A_BigGrassPoint_3</t>
         </is>
       </c>
       <c r="F117" s="8" t="n">
@@ -7668,11 +7668,11 @@
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 3</t>
+          <t>A 2번 방 큰 풀 4</t>
         </is>
       </c>
       <c r="C118" s="8" t="n">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_3</t>
+          <t>R02_A_BigGrassPoint_4</t>
         </is>
       </c>
       <c r="F118" s="8" t="n">
@@ -7704,11 +7704,11 @@
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 4</t>
+          <t>A 2번 방 큰 풀 5</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_4</t>
+          <t>R02_A_BigGrassPoint_5</t>
         </is>
       </c>
       <c r="F119" s="8" t="n">
@@ -7740,11 +7740,11 @@
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 5</t>
+          <t>A 2번 방 큰 풀 6</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_5</t>
+          <t>R02_A_BigGrassPoint_6</t>
         </is>
       </c>
       <c r="F120" s="8" t="n">
@@ -7776,11 +7776,11 @@
     </row>
     <row r="121">
       <c r="A121" s="8" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 6</t>
+          <t>A 2번 방 의자 1</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -7793,15 +7793,15 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_6</t>
+          <t>R02_A_ChairPoint_1</t>
         </is>
       </c>
       <c r="F121" s="8" t="n">
-        <v>13053</v>
+        <v>13050</v>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
+          <t>장식</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
@@ -7812,11 +7812,11 @@
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 1</t>
+          <t>A 2번 방 의자 2</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_1</t>
+          <t>R02_A_ChairPoint_2</t>
         </is>
       </c>
       <c r="F122" s="8" t="n">
@@ -7848,11 +7848,11 @@
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 2</t>
+          <t>A 2번 방 의자 3</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_2</t>
+          <t>R02_A_ChairPoint_3</t>
         </is>
       </c>
       <c r="F123" s="8" t="n">
@@ -7884,11 +7884,11 @@
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 3</t>
+          <t>A 2번 방 의자 4</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_3</t>
+          <t>R02_A_ChairPoint_4</t>
         </is>
       </c>
       <c r="F124" s="8" t="n">
@@ -7920,11 +7920,11 @@
     </row>
     <row r="125">
       <c r="A125" s="8" t="n">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 4</t>
+          <t>A 2번 방 조명 1</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
@@ -7937,11 +7937,11 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_4</t>
+          <t>R02_A_LightPoint_1</t>
         </is>
       </c>
       <c r="F125" s="8" t="n">
-        <v>13050</v>
+        <v>13051</v>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
@@ -7956,11 +7956,11 @@
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 1</t>
+          <t>A 2번 방 조명 2</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_1</t>
+          <t>R02_A_LightPoint_2</t>
         </is>
       </c>
       <c r="F126" s="8" t="n">
@@ -7992,11 +7992,11 @@
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 2</t>
+          <t>A 2번 방 조명 3</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_2</t>
+          <t>R02_A_LightPoint_3</t>
         </is>
       </c>
       <c r="F127" s="8" t="n">
@@ -8028,11 +8028,11 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 3</t>
+          <t>A 2번 방 조명 4</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_3</t>
+          <t>R02_A_LightPoint_4</t>
         </is>
       </c>
       <c r="F128" s="8" t="n">
@@ -8064,11 +8064,11 @@
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 4</t>
+          <t>A 2번 방 조명 5</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_4</t>
+          <t>R02_A_LightPoint_5</t>
         </is>
       </c>
       <c r="F129" s="8" t="n">
@@ -8100,11 +8100,11 @@
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 5</t>
+          <t>A 2번 방 조명 6</t>
         </is>
       </c>
       <c r="C130" s="8" t="n">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_5</t>
+          <t>R02_A_LightPoint_6</t>
         </is>
       </c>
       <c r="F130" s="8" t="n">
@@ -8136,11 +8136,11 @@
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 6</t>
+          <t>A 2번 방 조명 7</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_6</t>
+          <t>R02_A_LightPoint_7</t>
         </is>
       </c>
       <c r="F131" s="8" t="n">
@@ -8172,11 +8172,11 @@
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 7</t>
+          <t>A 2번 방 조명 8</t>
         </is>
       </c>
       <c r="C132" s="8" t="n">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_7</t>
+          <t>R02_A_LightPoint_8</t>
         </is>
       </c>
       <c r="F132" s="8" t="n">
@@ -8208,11 +8208,11 @@
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 8</t>
+          <t>B 2번 방 큰 풀 1</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
@@ -8220,16 +8220,16 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_8</t>
+          <t>R02_BigGrassPoint_1</t>
         </is>
       </c>
       <c r="F133" s="8" t="n">
-        <v>13051</v>
+        <v>13053</v>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
@@ -8244,11 +8244,11 @@
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 1</t>
+          <t>B 2번 방 큰 풀 2</t>
         </is>
       </c>
       <c r="C134" s="8" t="n">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_1</t>
+          <t>R02_BigGrassPoint_2</t>
         </is>
       </c>
       <c r="F134" s="8" t="n">
@@ -8280,11 +8280,11 @@
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 2</t>
+          <t>B 2번 방 큰 풀 3</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_2</t>
+          <t>R02_BigGrassPoint_3</t>
         </is>
       </c>
       <c r="F135" s="8" t="n">
@@ -8316,11 +8316,11 @@
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 3</t>
+          <t>B 2번 방 큰 풀 4</t>
         </is>
       </c>
       <c r="C136" s="8" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_3</t>
+          <t>R02_BigGrassPoint_4</t>
         </is>
       </c>
       <c r="F136" s="8" t="n">
@@ -8352,11 +8352,11 @@
     </row>
     <row r="137">
       <c r="A137" s="8" t="n">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 4</t>
+          <t>B 2번 방 큰 풀 5</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_4</t>
+          <t>R02_BigGrassPoint_5</t>
         </is>
       </c>
       <c r="F137" s="8" t="n">
@@ -8388,11 +8388,11 @@
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 5</t>
+          <t>B 2번 방 큰 풀 6</t>
         </is>
       </c>
       <c r="C138" s="8" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_5</t>
+          <t>R02_BigGrassPoint_6</t>
         </is>
       </c>
       <c r="F138" s="8" t="n">
@@ -8424,11 +8424,11 @@
     </row>
     <row r="139">
       <c r="A139" s="8" t="n">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 6</t>
+          <t>B 2번 방 큰 풀 7</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_6</t>
+          <t>R02_BigGrassPoint_7</t>
         </is>
       </c>
       <c r="F139" s="8" t="n">
@@ -8460,11 +8460,11 @@
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 7</t>
+          <t>B 2번 방 큰 풀 9</t>
         </is>
       </c>
       <c r="C140" s="8" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_7</t>
+          <t>R02_BigGrassPoint_9</t>
         </is>
       </c>
       <c r="F140" s="8" t="n">
@@ -8496,11 +8496,11 @@
     </row>
     <row r="141">
       <c r="A141" s="8" t="n">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 9</t>
+          <t>B 2번 방 큰 풀 10</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_9</t>
+          <t>R02_BigGrassPoint_10</t>
         </is>
       </c>
       <c r="F141" s="8" t="n">
@@ -8532,11 +8532,11 @@
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 10</t>
+          <t>B 2번 방 큰 풀 11</t>
         </is>
       </c>
       <c r="C142" s="8" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_10</t>
+          <t>R02_BigGrassPoint_11</t>
         </is>
       </c>
       <c r="F142" s="8" t="n">
@@ -8568,11 +8568,11 @@
     </row>
     <row r="143">
       <c r="A143" s="8" t="n">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 11</t>
+          <t>B 2번 방 작은 풀 1</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
@@ -8585,11 +8585,11 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_11</t>
+          <t>R02_SmallGrassPoint_1</t>
         </is>
       </c>
       <c r="F143" s="8" t="n">
-        <v>13053</v>
+        <v>13054</v>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
@@ -8604,11 +8604,11 @@
     </row>
     <row r="144">
       <c r="A144" s="8" t="n">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 작은 풀 1</t>
+          <t>B 2번 방 작은 풀 2</t>
         </is>
       </c>
       <c r="C144" s="8" t="n">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>R02_SmallGrassPoint_1</t>
+          <t>R02_SmallGrassPoint_2</t>
         </is>
       </c>
       <c r="F144" s="8" t="n">
@@ -8633,42 +8633,6 @@
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="8" t="n">
-        <v>2234</v>
-      </c>
-      <c r="B145" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 작은 풀 2</t>
-        </is>
-      </c>
-      <c r="C145" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D145" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t>R02_SmallGrassPoint_2</t>
-        </is>
-      </c>
-      <c r="F145" s="8" t="n">
-        <v>13054</v>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>장식</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -2676,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>R01_DoorPoint</t>
+          <t>R01_DoorModelPoint</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 문 프리팹 Door (모든 방 공통)</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 (문 모델 기준점). 문 프리팹 Door (모든 방 공통) / 이 앵커는 R01_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 출구 문</t>
+          <t>2번 방 출구 문 (A·B 공통, 2번→3번)</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>R2A_DOOR_OUT</t>
+          <t>R02_DoorModelPoint</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>출구. 방 ExitRule대로 열림</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래. 2번→3번 문틀 자리 (모델의 문 기준점과 같은 위치 · 회전). 문 프리팹 Door (모든 방 공통) / 이 앵커는 R02_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -3045,11 +3045,11 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>2008</v>
+        <v>2034</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 출구 문</t>
+          <t>A 2번 방 4칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -3057,22 +3057,18 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>R2B_DOOR_OUT</t>
+          <t>R2A_LOCK</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13005</v>
+      </c>
+      <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3081,15 +3077,15 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>2034</v>
+        <v>2010</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 4칸 다이얼 자물쇠</t>
+          <t>A 3번 방 출구 문</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
@@ -3098,13 +3094,17 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>R2A_LOCK</t>
+          <t>R3A_DOOR_OUT</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>13005</v>
-      </c>
-      <c r="G15" s="8" t="n"/>
+        <v>13002</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>출구. 방 ExitRule대로 열림</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3113,11 +3113,11 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 출구 문</t>
+          <t>B 3번 방 출구 문</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -3125,12 +3125,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>R3A_DOOR_OUT</t>
+          <t>R3B_DOOR_OUT</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
@@ -3149,11 +3149,11 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>2012</v>
+        <v>2039</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 출구 문</t>
+          <t>B 3번 방 화살표 콘솔</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -3166,17 +3166,13 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>R3B_DOOR_OUT</t>
+          <t>R3B_CONSOLE</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13012</v>
+      </c>
+      <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3185,30 +3181,34 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>2039</v>
+        <v>2014</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 화살표 콘솔</t>
+          <t>A 4번 방 출구 문</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>R3B_CONSOLE</t>
+          <t>R4A_DOOR_OUT</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>13012</v>
-      </c>
-      <c r="G18" s="8" t="n"/>
+        <v>13002</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>출구. 방 ExitRule대로 열림</t>
+        </is>
+      </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3217,11 +3217,11 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 출구 문</t>
+          <t>B 4번 방 출구 문</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>R4A_DOOR_OUT</t>
+          <t>R4B_DOOR_OUT</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
@@ -3253,11 +3253,11 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2016</v>
+        <v>2042</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 출구 문</t>
+          <t>A 4번 방 5칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
@@ -3265,22 +3265,18 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>R4B_DOOR_OUT</t>
+          <t>R4A_LOCK</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13006</v>
+      </c>
+      <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3289,11 +3285,11 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 5칸 다이얼 자물쇠</t>
+          <t>B 4번 방 배선 콘솔</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -3301,18 +3297,22 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>R4A_LOCK</t>
+          <t>R4B_CONSOLE</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>13006</v>
-      </c>
-      <c r="G21" s="8" t="n"/>
+        <v>13013</v>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>받침대 R4B_CONSOLE_STAND 위. 클릭하면 조작 화면이 열리고 뚜껑이 열려 안쪽 전선이 보임</t>
+        </is>
+      </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3321,32 +3321,32 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2044</v>
+        <v>2018</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 배선 콘솔</t>
+          <t>A 5번 방 출구 문</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>R4B_CONSOLE</t>
+          <t>R5A_DOOR_OUT</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>13013</v>
+        <v>13002</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>받침대 R4B_CONSOLE_STAND 위. 클릭하면 조작 화면이 열리고 뚜껑이 열려 안쪽 전선이 보임</t>
+          <t>출구. 방 ExitRule대로 열림</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -3357,11 +3357,11 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 출구 문</t>
+          <t>B 5번 방 출구 문</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>R5A_DOOR_OUT</t>
+          <t>R5B_DOOR_OUT</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
@@ -3393,11 +3393,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2020</v>
+        <v>2051</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 출구 문</t>
+          <t>B 5번 방 4칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -3410,15 +3410,15 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>R5B_DOOR_OUT</t>
+          <t>R5B_LOCK</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13002</v>
+        <v>13005</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>출구. 방 ExitRule대로 열림</t>
+          <t>C는 다이얼 2칸(십의 자리, 일의 자리)</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -3429,32 +3429,32 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>2051</v>
+        <v>2022</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 4칸 다이얼 자물쇠</t>
+          <t>A 6번 방 출구 문</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>R5B_LOCK</t>
+          <t>R6A_DOOR_OUT</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>C는 다이얼 2칸(십의 자리, 일의 자리)</t>
+          <t>출구. 방 ExitRule대로 열림</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -3465,11 +3465,11 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 출구 문</t>
+          <t>B 6번 방 출구 문</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>R6A_DOOR_OUT</t>
+          <t>R6B_DOOR_OUT</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
@@ -3501,11 +3501,11 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>2024</v>
+        <v>2054</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 출구 문</t>
+          <t>A 6번 방 5칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -3513,20 +3513,20 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>R6B_DOOR_OUT</t>
+          <t>R6A_LOCK</t>
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>13002</v>
+        <v>13006</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>출구. 방 ExitRule대로 열림</t>
+          <t>다이얼마다 정답 글자를 포함한 9자 고정</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -3537,15 +3537,15 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>2054</v>
+        <v>2026</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 5칸 다이얼 자물쇠</t>
+          <t>A 7번 방 출구 문</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
@@ -3554,15 +3554,15 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>R6A_LOCK</t>
+          <t>R7A_DOOR_OUT</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>13006</v>
+        <v>13002</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>다이얼마다 정답 글자를 포함한 9자 고정</t>
+          <t>출구. 방 ExitRule대로 열림</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -3573,11 +3573,11 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>A 7번 방 출구 문</t>
+          <t>B 7번 방 출구 문</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>R7A_DOOR_OUT</t>
+          <t>R7B_DOOR_OUT</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
@@ -3609,11 +3609,11 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>2028</v>
+        <v>2071</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>B 7번 방 출구 문</t>
+          <t>A 7번 방 6칸 색 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -3621,22 +3621,18 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>R7B_DOOR_OUT</t>
+          <t>R7A_LOCK</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13007</v>
+      </c>
+      <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3645,11 +3641,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>A 7번 방 6칸 색 다이얼 자물쇠</t>
+          <t>B 7번 방 6칸 색 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -3657,12 +3653,12 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>R7A_LOCK</t>
+          <t>R7B_LOCK</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
@@ -3670,38 +3666,6 @@
       </c>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>2073</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>B 7번 방 6칸 색 다이얼 자물쇠</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>R7B_LOCK</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>13007</v>
-      </c>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3735,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -4237,12 +4201,12 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -4273,12 +4237,12 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: 기본 방(Room_01_Final)에 천장 포함 · 꺼둠</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4309,12 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문 / R01_v3: 기본 방(Room_01_Final)에 dver' 포함 · 꺼둠</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -4381,26 +4345,26 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로</t>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2033</v>
+        <v>2249</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 테이블</t>
+          <t>A 1번 방 소품 (서랍장 · 바닥 카드, Room_01_Final 1)</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
@@ -4409,13 +4373,17 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>R02_A_TablePoint</t>
+          <t>R01A_PropsPoint</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>13052</v>
-      </c>
-      <c r="G22" s="8" t="n"/>
+        <v>13075</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래. 방 원점 (0,0,0), 회전 없음: Room_01_Final 1 안 모델들이 방 기준 절대 위치로 저장돼 있어 원점에 두면 제자리에 놓임. B는 생성 안 함</t>
+        </is>
+      </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4424,11 +4392,11 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 글자 표시판</t>
+          <t>A 2번 방 테이블</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -4441,26 +4409,30 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>R2A_SIGN</t>
+          <t>R02_A_TablePoint</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G23" s="8" t="n"/>
+        <v>13052</v>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음).</t>
+        </is>
+      </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2125</v>
+        <v>2035</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 01</t>
+          <t>A 2번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -4468,22 +4440,18 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>R02_RedFramePoint_1</t>
+          <t>R2A_SIGN</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13063</v>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>색 Red</t>
-        </is>
-      </c>
+        <v>13008</v>
+      </c>
+      <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4492,11 +4460,11 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 02</t>
+          <t>B 2번 방 액자 01</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -4509,7 +4477,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>R02_RedFramePoint_2</t>
+          <t>R02_RedFramePoint_1</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
@@ -4517,22 +4485,22 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>색 Red</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Red</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 03</t>
+          <t>B 2번 방 액자 02</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -4545,30 +4513,30 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>R02_BlueFramePoint_2</t>
+          <t>R02_RedFramePoint_2</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13056</v>
+        <v>13063</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>색 Blue</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Red</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 04</t>
+          <t>B 2번 방 액자 03</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -4581,30 +4549,30 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_4</t>
+          <t>R02_BlueFramePoint_2</t>
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>13064</v>
+        <v>13056</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Blue</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 05</t>
+          <t>B 2번 방 액자 04</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -4617,30 +4585,30 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_1</t>
+          <t>R02_YellowFramePoint_4</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>13058</v>
+        <v>13064</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>색 Green</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Yellow</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 06</t>
+          <t>B 2번 방 액자 05</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -4653,7 +4621,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_2</t>
+          <t>R02_GreenFramePoint_1</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
@@ -4661,22 +4629,22 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>색 Green. Unity 이름에 공백('R02_GreenFramePoint _2'), 표에는 공백 없이 씀</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Green</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 07</t>
+          <t>B 2번 방 액자 06</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -4689,7 +4657,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_3</t>
+          <t>R02_GreenFramePoint_2</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
@@ -4697,22 +4665,22 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>색 Green</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Green. Unity 이름에 공백('R02_GreenFramePoint _2'), 표에는 공백 없이 씀</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 08</t>
+          <t>B 2번 방 액자 07</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -4725,7 +4693,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>R02_GreenFramePoint_4</t>
+          <t>R02_GreenFramePoint_3</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
@@ -4733,22 +4701,22 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>색 Green</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Green</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 09</t>
+          <t>B 2번 방 액자 08</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -4761,30 +4729,30 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>R02_BlackFramePoint_2</t>
+          <t>R02_GreenFramePoint_4</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>13055</v>
+        <v>13058</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>색 Black</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Green</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 10</t>
+          <t>B 2번 방 액자 09</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -4797,30 +4765,30 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_3</t>
+          <t>R02_BlackFramePoint_2</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>13062</v>
+        <v>13055</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Black</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 11</t>
+          <t>B 2번 방 액자 10</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -4833,7 +4801,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_4</t>
+          <t>R02_PuppleFreamPoint_3</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
@@ -4841,22 +4809,22 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 12</t>
+          <t>B 2번 방 액자 11</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -4869,30 +4837,30 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_2</t>
+          <t>R02_PuppleFreamPoint_4</t>
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>13060</v>
+        <v>13062</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>색 Navy</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 13</t>
+          <t>B 2번 방 액자 12</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -4905,7 +4873,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_3</t>
+          <t>R02_NavyFreamPoint_2</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
@@ -4913,22 +4881,22 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>색 Navy</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Navy</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 14</t>
+          <t>B 2번 방 액자 13</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -4941,30 +4909,30 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>R02_BlueFramePoint_1</t>
+          <t>R02_NavyFreamPoint_3</t>
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>13056</v>
+        <v>13060</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>색 Blue</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Navy</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 15</t>
+          <t>B 2번 방 액자 14</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -4977,30 +4945,30 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>R02_GrayFramePoint_1</t>
+          <t>R02_BlueFramePoint_1</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>13057</v>
+        <v>13056</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>색 Gray</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Blue</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 16</t>
+          <t>B 2번 방 액자 15</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -5013,7 +4981,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>R02_GrayFramePoint_2</t>
+          <t>R02_GrayFramePoint_1</t>
         </is>
       </c>
       <c r="F39" s="8" t="n">
@@ -5021,22 +4989,22 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>색 Gray</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Gray</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 17</t>
+          <t>B 2번 방 액자 16</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -5049,30 +5017,30 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_1</t>
+          <t>R02_GrayFramePoint_2</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>13064</v>
+        <v>13057</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Gray</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 18</t>
+          <t>B 2번 방 액자 17</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -5085,7 +5053,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_2</t>
+          <t>R02_YellowFramePoint_1</t>
         </is>
       </c>
       <c r="F41" s="8" t="n">
@@ -5093,22 +5061,22 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Yellow</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 19</t>
+          <t>B 2번 방 액자 18</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -5121,7 +5089,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>R02_YellowFramePoint_3</t>
+          <t>R02_YellowFramePoint_2</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
@@ -5129,22 +5097,22 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>색 Yellow</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Yellow</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 20</t>
+          <t>B 2번 방 액자 19</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -5157,30 +5125,30 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>R02_OrangeFreamPoint_1</t>
+          <t>R02_YellowFramePoint_3</t>
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>13061</v>
+        <v>13064</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>색 Orange</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Yellow</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 21</t>
+          <t>B 2번 방 액자 20</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -5193,7 +5161,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>R02_OrangeFreamPoint_2</t>
+          <t>R02_OrangeFreamPoint_1</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
@@ -5201,22 +5169,22 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>색 Orange</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Orange</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 22</t>
+          <t>B 2번 방 액자 21</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -5229,30 +5197,30 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>R02_BlackFramePoint_1</t>
+          <t>R02_OrangeFreamPoint_2</t>
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>13055</v>
+        <v>13061</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>색 Black</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Orange</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 23</t>
+          <t>B 2번 방 액자 22</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -5265,30 +5233,30 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_1</t>
+          <t>R02_BlackFramePoint_1</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>13062</v>
+        <v>13055</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Black</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 24</t>
+          <t>B 2번 방 액자 23</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -5301,7 +5269,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>R02_PuppleFreamPoint_2</t>
+          <t>R02_PuppleFreamPoint_1</t>
         </is>
       </c>
       <c r="F47" s="8" t="n">
@@ -5309,22 +5277,22 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>색 Purple (Unity 프리팹 이름은 Pupple)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 25</t>
+          <t>B 2번 방 액자 24</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -5337,30 +5305,30 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>R02_MintFramePoint_1</t>
+          <t>R02_PuppleFreamPoint_2</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>13059</v>
+        <v>13062</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Purple (Unity 프리팹 이름은 Pupple)</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 26</t>
+          <t>B 2번 방 액자 25</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -5373,7 +5341,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>R02_MintFramePoint_2</t>
+          <t>R02_MintFramePoint_1</t>
         </is>
       </c>
       <c r="F49" s="8" t="n">
@@ -5381,22 +5349,22 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>색 Teal (Unity 프리팹 이름은 Mint)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Teal (Unity 프리팹 이름은 Mint)</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 액자 28</t>
+          <t>B 2번 방 액자 26</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -5409,34 +5377,34 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>R02_NavyFreamPoint_1</t>
+          <t>R02_MintFramePoint_2</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>13060</v>
+        <v>13059</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>색 Navy</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Teal (Unity 프리팹 이름은 Mint)</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>2040</v>
+        <v>2152</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 글자 표시판</t>
+          <t>B 2번 방 액자 28</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
@@ -5445,26 +5413,30 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>R3B_SIGN</t>
+          <t>R02_NavyFreamPoint_1</t>
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G51" s="8" t="n"/>
+        <v>13060</v>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 색 Navy</t>
+        </is>
+      </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>2183</v>
+        <v>2040</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 01</t>
+          <t>B 3번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -5472,22 +5444,18 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_01</t>
+          <t>R3B_SIGN</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>13011</v>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
-        </is>
-      </c>
+        <v>13008</v>
+      </c>
+      <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5496,11 +5464,11 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 02</t>
+          <t>A 3번 방 단서 화살표 01</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -5513,7 +5481,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_02</t>
+          <t>R3A_ARROW_01</t>
         </is>
       </c>
       <c r="F53" s="8" t="n">
@@ -5521,7 +5489,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -5532,11 +5500,11 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 03</t>
+          <t>A 3번 방 단서 화살표 02</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -5549,7 +5517,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_03</t>
+          <t>R3A_ARROW_02</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
@@ -5557,7 +5525,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -5568,11 +5536,11 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 04</t>
+          <t>A 3번 방 단서 화살표 03</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -5585,7 +5553,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_04</t>
+          <t>R3A_ARROW_03</t>
         </is>
       </c>
       <c r="F55" s="8" t="n">
@@ -5593,7 +5561,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -5604,11 +5572,11 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 05</t>
+          <t>A 3번 방 단서 화살표 04</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -5621,7 +5589,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_05</t>
+          <t>R3A_ARROW_04</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
@@ -5629,7 +5597,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -5640,11 +5608,11 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 06</t>
+          <t>A 3번 방 단서 화살표 05</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -5657,7 +5625,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_06</t>
+          <t>R3A_ARROW_05</t>
         </is>
       </c>
       <c r="F57" s="8" t="n">
@@ -5665,7 +5633,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -5676,11 +5644,11 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 07</t>
+          <t>A 3번 방 단서 화살표 06</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -5693,7 +5661,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_07</t>
+          <t>R3A_ARROW_06</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
@@ -5701,7 +5669,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -5712,11 +5680,11 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 08</t>
+          <t>A 3번 방 단서 화살표 07</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -5729,7 +5697,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_08</t>
+          <t>R3A_ARROW_07</t>
         </is>
       </c>
       <c r="F59" s="8" t="n">
@@ -5737,7 +5705,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -5748,11 +5716,11 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 09</t>
+          <t>A 3번 방 단서 화살표 08</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -5765,7 +5733,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_09</t>
+          <t>R3A_ARROW_08</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
@@ -5773,7 +5741,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -5784,11 +5752,11 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 단서 화살표 10</t>
+          <t>A 3번 방 단서 화살표 09</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -5801,7 +5769,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>R3A_ARROW_10</t>
+          <t>R3A_ARROW_09</t>
         </is>
       </c>
       <c r="F61" s="8" t="n">
@@ -5809,7 +5777,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -5820,15 +5788,15 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>2041</v>
+        <v>2192</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 테이블</t>
+          <t>A 3번 방 단서 화살표 10</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
@@ -5837,13 +5805,17 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>R4A_TABLE</t>
+          <t>R3A_ARROW_10</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>13003</v>
-      </c>
-      <c r="G62" s="8" t="n"/>
+        <v>13011</v>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
+        </is>
+      </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5852,11 +5824,11 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 글자 표시판</t>
+          <t>A 4번 방 테이블</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -5869,11 +5841,11 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>R4A_SIGN</t>
+          <t>R4A_TABLE</t>
         </is>
       </c>
       <c r="F63" s="8" t="n">
-        <v>13008</v>
+        <v>13003</v>
       </c>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="inlineStr">
@@ -5884,11 +5856,11 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>2074</v>
+        <v>2043</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 배선 콘솔 받침대</t>
+          <t>A 4번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -5896,22 +5868,18 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>R4B_CONSOLE_STAND</t>
+          <t>R4A_SIGN</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>13019</v>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
-        </is>
-      </c>
+        <v>13008</v>
+      </c>
+      <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5920,11 +5888,11 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>2153</v>
+        <v>2074</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 01 (정답)</t>
+          <t>B 4번 방 배선 콘솔 받침대</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -5937,15 +5905,15 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_01</t>
+          <t>R4B_CONSOLE_STAND</t>
         </is>
       </c>
       <c r="F65" s="8" t="n">
-        <v>13034</v>
+        <v>13019</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -5956,11 +5924,11 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 02 (정답)</t>
+          <t>B 4번 방 전선 01 (정답)</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -5973,7 +5941,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_02</t>
+          <t>R4B_WIRE_01</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
@@ -5992,11 +5960,11 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 03 (정답)</t>
+          <t>B 4번 방 전선 02 (정답)</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -6009,7 +5977,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_03</t>
+          <t>R4B_WIRE_02</t>
         </is>
       </c>
       <c r="F67" s="8" t="n">
@@ -6028,11 +5996,11 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 04 (정답)</t>
+          <t>B 4번 방 전선 03 (정답)</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -6045,7 +6013,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_04</t>
+          <t>R4B_WIRE_03</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
@@ -6064,11 +6032,11 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 05 (정답)</t>
+          <t>B 4번 방 전선 04 (정답)</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -6081,7 +6049,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_05</t>
+          <t>R4B_WIRE_04</t>
         </is>
       </c>
       <c r="F69" s="8" t="n">
@@ -6100,11 +6068,11 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 06 (가짜)</t>
+          <t>B 4번 방 전선 05 (정답)</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -6117,7 +6085,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_06</t>
+          <t>R4B_WIRE_05</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
@@ -6136,11 +6104,11 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 07 (가짜)</t>
+          <t>B 4번 방 전선 06 (가짜)</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -6153,7 +6121,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_07</t>
+          <t>R4B_WIRE_06</t>
         </is>
       </c>
       <c r="F71" s="8" t="n">
@@ -6172,11 +6140,11 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 08 (가짜)</t>
+          <t>B 4번 방 전선 07 (가짜)</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -6189,7 +6157,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_08</t>
+          <t>R4B_WIRE_07</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
@@ -6208,11 +6176,11 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 09 (가짜)</t>
+          <t>B 4번 방 전선 08 (가짜)</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -6225,7 +6193,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_09</t>
+          <t>R4B_WIRE_08</t>
         </is>
       </c>
       <c r="F73" s="8" t="n">
@@ -6244,11 +6212,11 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 전선 10 (가짜)</t>
+          <t>B 4번 방 전선 09 (가짜)</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -6261,7 +6229,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>R4B_WIRE_10</t>
+          <t>R4B_WIRE_09</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
@@ -6280,30 +6248,34 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>2048</v>
+        <v>2162</v>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 테이블</t>
+          <t>B 4번 방 전선 10 (가짜)</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>R5A_TABLE</t>
+          <t>R4B_WIRE_10</t>
         </is>
       </c>
       <c r="F75" s="8" t="n">
-        <v>13003</v>
-      </c>
-      <c r="G75" s="8" t="n"/>
+        <v>13034</v>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>배선 콘솔 안 단자에 연결</t>
+        </is>
+      </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6312,11 +6284,11 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 종이</t>
+          <t>A 5번 방 테이블</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
@@ -6329,11 +6301,11 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>R5A_PAPER</t>
+          <t>R5A_TABLE</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>13016</v>
+        <v>13003</v>
       </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="inlineStr">
@@ -6344,11 +6316,11 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 자물쇠 받침대</t>
+          <t>A 5번 방 종이</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -6356,16 +6328,16 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>R5B_STAND</t>
+          <t>R5A_PAPER</t>
         </is>
       </c>
       <c r="F77" s="8" t="n">
-        <v>13004</v>
+        <v>13016</v>
       </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
@@ -6376,11 +6348,11 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 글자 표시판</t>
+          <t>B 5번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -6393,11 +6365,11 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>R5B_SIGN</t>
+          <t>R5B_STAND</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>13008</v>
+        <v>13004</v>
       </c>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="inlineStr">
@@ -6408,11 +6380,11 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>2163</v>
+        <v>2052</v>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 01 (진짜 정의)</t>
+          <t>B 5번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -6420,16 +6392,16 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_01</t>
+          <t>R5B_SIGN</t>
         </is>
       </c>
       <c r="F79" s="8" t="n">
-        <v>13014</v>
+        <v>13008</v>
       </c>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="inlineStr">
@@ -6440,11 +6412,11 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 02</t>
+          <t>A 5번 방 공식판 01 (진짜 정의)</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -6457,7 +6429,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_02</t>
+          <t>R5A_FORMULA_01</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
@@ -6472,11 +6444,11 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 03</t>
+          <t>A 5번 방 공식판 02</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -6489,7 +6461,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_03</t>
+          <t>R5A_FORMULA_02</t>
         </is>
       </c>
       <c r="F81" s="8" t="n">
@@ -6504,11 +6476,11 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 04</t>
+          <t>A 5번 방 공식판 03</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -6521,7 +6493,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_04</t>
+          <t>R5A_FORMULA_03</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
@@ -6536,11 +6508,11 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 05</t>
+          <t>A 5번 방 공식판 04</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -6553,7 +6525,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_05</t>
+          <t>R5A_FORMULA_04</t>
         </is>
       </c>
       <c r="F83" s="8" t="n">
@@ -6568,11 +6540,11 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 06</t>
+          <t>A 5번 방 공식판 05</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -6585,7 +6557,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_06</t>
+          <t>R5A_FORMULA_05</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
@@ -6600,11 +6572,11 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 07</t>
+          <t>A 5번 방 공식판 06</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -6617,7 +6589,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_07</t>
+          <t>R5A_FORMULA_06</t>
         </is>
       </c>
       <c r="F85" s="8" t="n">
@@ -6632,11 +6604,11 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 08</t>
+          <t>A 5번 방 공식판 07</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -6649,7 +6621,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_08</t>
+          <t>R5A_FORMULA_07</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
@@ -6664,11 +6636,11 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 09</t>
+          <t>A 5번 방 공식판 08</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -6681,7 +6653,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_09</t>
+          <t>R5A_FORMULA_08</t>
         </is>
       </c>
       <c r="F87" s="8" t="n">
@@ -6696,11 +6668,11 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 10</t>
+          <t>A 5번 방 공식판 09</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -6713,7 +6685,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_10</t>
+          <t>R5A_FORMULA_09</t>
         </is>
       </c>
       <c r="F88" s="8" t="n">
@@ -6728,11 +6700,11 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 11</t>
+          <t>A 5번 방 공식판 10</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -6745,7 +6717,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_11</t>
+          <t>R5A_FORMULA_10</t>
         </is>
       </c>
       <c r="F89" s="8" t="n">
@@ -6760,11 +6732,11 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 12</t>
+          <t>A 5번 방 공식판 11</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -6777,7 +6749,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_12</t>
+          <t>R5A_FORMULA_11</t>
         </is>
       </c>
       <c r="F90" s="8" t="n">
@@ -6792,11 +6764,11 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 13</t>
+          <t>A 5번 방 공식판 12</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -6809,7 +6781,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_13</t>
+          <t>R5A_FORMULA_12</t>
         </is>
       </c>
       <c r="F91" s="8" t="n">
@@ -6824,11 +6796,11 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 14</t>
+          <t>A 5번 방 공식판 13</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -6841,7 +6813,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_14</t>
+          <t>R5A_FORMULA_13</t>
         </is>
       </c>
       <c r="F92" s="8" t="n">
@@ -6856,11 +6828,11 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 15</t>
+          <t>A 5번 방 공식판 14</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -6873,7 +6845,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_15</t>
+          <t>R5A_FORMULA_14</t>
         </is>
       </c>
       <c r="F93" s="8" t="n">
@@ -6888,11 +6860,11 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 16</t>
+          <t>A 5번 방 공식판 15</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -6905,7 +6877,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_16</t>
+          <t>R5A_FORMULA_15</t>
         </is>
       </c>
       <c r="F94" s="8" t="n">
@@ -6920,11 +6892,11 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 17</t>
+          <t>A 5번 방 공식판 16</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -6937,7 +6909,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_17</t>
+          <t>R5A_FORMULA_16</t>
         </is>
       </c>
       <c r="F95" s="8" t="n">
@@ -6952,11 +6924,11 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 18</t>
+          <t>A 5번 방 공식판 17</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -6969,7 +6941,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_18</t>
+          <t>R5A_FORMULA_17</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
@@ -6984,11 +6956,11 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 19</t>
+          <t>A 5번 방 공식판 18</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -7001,7 +6973,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_19</t>
+          <t>R5A_FORMULA_18</t>
         </is>
       </c>
       <c r="F97" s="8" t="n">
@@ -7016,11 +6988,11 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 공식판 20</t>
+          <t>A 5번 방 공식판 19</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -7033,7 +7005,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>R5A_FORMULA_20</t>
+          <t>R5A_FORMULA_19</t>
         </is>
       </c>
       <c r="F98" s="8" t="n">
@@ -7048,15 +7020,15 @@
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>2053</v>
+        <v>2182</v>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 자물쇠 받침대</t>
+          <t>A 5번 방 공식판 20</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
@@ -7065,11 +7037,11 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>R6A_STAND</t>
+          <t>R5A_FORMULA_20</t>
         </is>
       </c>
       <c r="F99" s="8" t="n">
-        <v>13004</v>
+        <v>13014</v>
       </c>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="inlineStr">
@@ -7080,11 +7052,11 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 글자 표시판</t>
+          <t>A 6번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
@@ -7097,11 +7069,11 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>R6A_SIGN</t>
+          <t>R6A_STAND</t>
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>13008</v>
+        <v>13004</v>
       </c>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="inlineStr">
@@ -7112,11 +7084,11 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 켜진 TV</t>
+          <t>A 6번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -7124,16 +7096,16 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N01</t>
+          <t>R6A_SIGN</t>
         </is>
       </c>
       <c r="F101" s="8" t="n">
-        <v>13017</v>
+        <v>13008</v>
       </c>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="inlineStr">
@@ -7144,7 +7116,7 @@
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
@@ -7161,7 +7133,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N02</t>
+          <t>R6B_TV_N01</t>
         </is>
       </c>
       <c r="F102" s="8" t="n">
@@ -7176,7 +7148,7 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
@@ -7193,7 +7165,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N03</t>
+          <t>R6B_TV_N02</t>
         </is>
       </c>
       <c r="F103" s="8" t="n">
@@ -7208,7 +7180,7 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
@@ -7225,7 +7197,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N04</t>
+          <t>R6B_TV_N03</t>
         </is>
       </c>
       <c r="F104" s="8" t="n">
@@ -7240,7 +7212,7 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
@@ -7257,7 +7229,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N05</t>
+          <t>R6B_TV_N04</t>
         </is>
       </c>
       <c r="F105" s="8" t="n">
@@ -7272,7 +7244,7 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
@@ -7289,7 +7261,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_N06</t>
+          <t>R6B_TV_N05</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
@@ -7304,7 +7276,7 @@
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
@@ -7321,7 +7293,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S01</t>
+          <t>R6B_TV_N06</t>
         </is>
       </c>
       <c r="F107" s="8" t="n">
@@ -7336,7 +7308,7 @@
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
@@ -7353,7 +7325,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S02</t>
+          <t>R6B_TV_S01</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
@@ -7368,7 +7340,7 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
@@ -7385,7 +7357,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S03</t>
+          <t>R6B_TV_S02</t>
         </is>
       </c>
       <c r="F109" s="8" t="n">
@@ -7400,7 +7372,7 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
@@ -7417,7 +7389,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S04</t>
+          <t>R6B_TV_S03</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
@@ -7432,7 +7404,7 @@
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
@@ -7449,7 +7421,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S05</t>
+          <t>R6B_TV_S04</t>
         </is>
       </c>
       <c r="F111" s="8" t="n">
@@ -7464,7 +7436,7 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
@@ -7481,7 +7453,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>R6B_TV_S06</t>
+          <t>R6B_TV_S05</t>
         </is>
       </c>
       <c r="F112" s="8" t="n">
@@ -7496,28 +7468,28 @@
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>A 7번 방 자물쇠 받침대</t>
+          <t>B 6번 방 켜진 TV</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>R7A_STAND</t>
+          <t>R6B_TV_S06</t>
         </is>
       </c>
       <c r="F113" s="8" t="n">
-        <v>13004</v>
+        <v>13017</v>
       </c>
       <c r="G113" s="8" t="n"/>
       <c r="H113" s="8" t="inlineStr">
@@ -7528,11 +7500,11 @@
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>B 7번 방 자물쇠 받침대</t>
+          <t>A 7번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
@@ -7540,12 +7512,12 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>R7B_STAND</t>
+          <t>R7A_STAND</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
@@ -7560,34 +7532,30 @@
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
-        <v>2205</v>
+        <v>2072</v>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 1</t>
+          <t>B 7번 방 자물쇠 받침대</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_1</t>
+          <t>R7B_STAND</t>
         </is>
       </c>
       <c r="F115" s="8" t="n">
-        <v>13053</v>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
-        </is>
-      </c>
+        <v>13004</v>
+      </c>
+      <c r="G115" s="8" t="n"/>
       <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7596,11 +7564,11 @@
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 2</t>
+          <t>A 2번 방 큰 풀 1</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -7613,7 +7581,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_2</t>
+          <t>R02_A_BigGrassPoint_1</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
@@ -7621,22 +7589,22 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 3</t>
+          <t>A 2번 방 큰 풀 2</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
@@ -7649,7 +7617,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_3</t>
+          <t>R02_A_BigGrassPoint_2</t>
         </is>
       </c>
       <c r="F117" s="8" t="n">
@@ -7657,22 +7625,22 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 4</t>
+          <t>A 2번 방 큰 풀 3</t>
         </is>
       </c>
       <c r="C118" s="8" t="n">
@@ -7685,7 +7653,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_4</t>
+          <t>R02_A_BigGrassPoint_3</t>
         </is>
       </c>
       <c r="F118" s="8" t="n">
@@ -7693,22 +7661,22 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 5</t>
+          <t>A 2번 방 큰 풀 4</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
@@ -7721,7 +7689,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_5</t>
+          <t>R02_A_BigGrassPoint_4</t>
         </is>
       </c>
       <c r="F119" s="8" t="n">
@@ -7729,22 +7697,22 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 큰 풀 6</t>
+          <t>A 2번 방 큰 풀 5</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
@@ -7757,7 +7725,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>R02_A_BigGrassPoint_6</t>
+          <t>R02_A_BigGrassPoint_5</t>
         </is>
       </c>
       <c r="F120" s="8" t="n">
@@ -7765,22 +7733,22 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 1</t>
+          <t>A 2번 방 큰 풀 6</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -7793,30 +7761,30 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_1</t>
+          <t>R02_A_BigGrassPoint_6</t>
         </is>
       </c>
       <c r="F121" s="8" t="n">
-        <v>13050</v>
+        <v>13053</v>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식 (B 방 큰 풀 프리팹을 같이 씀)</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 2</t>
+          <t>A 2번 방 의자 1</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -7829,7 +7797,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_2</t>
+          <t>R02_A_ChairPoint_1</t>
         </is>
       </c>
       <c r="F122" s="8" t="n">
@@ -7837,22 +7805,22 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 3</t>
+          <t>A 2번 방 의자 2</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
@@ -7865,7 +7833,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_3</t>
+          <t>R02_A_ChairPoint_2</t>
         </is>
       </c>
       <c r="F123" s="8" t="n">
@@ -7873,22 +7841,22 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 의자 4</t>
+          <t>A 2번 방 의자 3</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
@@ -7901,7 +7869,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>R02_A_ChairPoint_4</t>
+          <t>R02_A_ChairPoint_3</t>
         </is>
       </c>
       <c r="F124" s="8" t="n">
@@ -7909,22 +7877,22 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="n">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 1</t>
+          <t>A 2번 방 의자 4</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
@@ -7937,30 +7905,30 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_1</t>
+          <t>R02_A_ChairPoint_4</t>
         </is>
       </c>
       <c r="F125" s="8" t="n">
-        <v>13051</v>
+        <v>13050</v>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 2</t>
+          <t>A 2번 방 조명 1</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
@@ -7973,7 +7941,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_2</t>
+          <t>R02_A_LightPoint_1</t>
         </is>
       </c>
       <c r="F126" s="8" t="n">
@@ -7981,22 +7949,22 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 3</t>
+          <t>A 2번 방 조명 2</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -8009,7 +7977,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_3</t>
+          <t>R02_A_LightPoint_2</t>
         </is>
       </c>
       <c r="F127" s="8" t="n">
@@ -8017,22 +7985,22 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 4</t>
+          <t>A 2번 방 조명 3</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">
@@ -8045,7 +8013,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_4</t>
+          <t>R02_A_LightPoint_3</t>
         </is>
       </c>
       <c r="F128" s="8" t="n">
@@ -8053,22 +8021,22 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 5</t>
+          <t>A 2번 방 조명 4</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
@@ -8081,7 +8049,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_5</t>
+          <t>R02_A_LightPoint_4</t>
         </is>
       </c>
       <c r="F129" s="8" t="n">
@@ -8089,22 +8057,22 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 6</t>
+          <t>A 2번 방 조명 5</t>
         </is>
       </c>
       <c r="C130" s="8" t="n">
@@ -8117,7 +8085,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_6</t>
+          <t>R02_A_LightPoint_5</t>
         </is>
       </c>
       <c r="F130" s="8" t="n">
@@ -8125,22 +8093,22 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 7</t>
+          <t>A 2번 방 조명 6</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
@@ -8153,7 +8121,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_7</t>
+          <t>R02_A_LightPoint_6</t>
         </is>
       </c>
       <c r="F131" s="8" t="n">
@@ -8161,22 +8129,22 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 조명 8</t>
+          <t>A 2번 방 조명 7</t>
         </is>
       </c>
       <c r="C132" s="8" t="n">
@@ -8189,7 +8157,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>R02_A_LightPoint_8</t>
+          <t>R02_A_LightPoint_7</t>
         </is>
       </c>
       <c r="F132" s="8" t="n">
@@ -8197,22 +8165,22 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 1</t>
+          <t>A 2번 방 조명 8</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
@@ -8220,35 +8188,35 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_1</t>
+          <t>R02_A_LightPoint_8</t>
         </is>
       </c>
       <c r="F133" s="8" t="n">
-        <v>13053</v>
+        <v>13051</v>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 2</t>
+          <t>B 2번 방 큰 풀 1</t>
         </is>
       </c>
       <c r="C134" s="8" t="n">
@@ -8261,7 +8229,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_2</t>
+          <t>R02_BigGrassPoint_1</t>
         </is>
       </c>
       <c r="F134" s="8" t="n">
@@ -8269,22 +8237,22 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 3</t>
+          <t>B 2번 방 큰 풀 2</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
@@ -8297,7 +8265,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_3</t>
+          <t>R02_BigGrassPoint_2</t>
         </is>
       </c>
       <c r="F135" s="8" t="n">
@@ -8305,22 +8273,22 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 4</t>
+          <t>B 2번 방 큰 풀 3</t>
         </is>
       </c>
       <c r="C136" s="8" t="n">
@@ -8333,7 +8301,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_4</t>
+          <t>R02_BigGrassPoint_3</t>
         </is>
       </c>
       <c r="F136" s="8" t="n">
@@ -8341,22 +8309,22 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="n">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 5</t>
+          <t>B 2번 방 큰 풀 4</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
@@ -8369,7 +8337,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_5</t>
+          <t>R02_BigGrassPoint_4</t>
         </is>
       </c>
       <c r="F137" s="8" t="n">
@@ -8377,22 +8345,22 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 6</t>
+          <t>B 2번 방 큰 풀 5</t>
         </is>
       </c>
       <c r="C138" s="8" t="n">
@@ -8405,7 +8373,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_6</t>
+          <t>R02_BigGrassPoint_5</t>
         </is>
       </c>
       <c r="F138" s="8" t="n">
@@ -8413,22 +8381,22 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="n">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 7</t>
+          <t>B 2번 방 큰 풀 6</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
@@ -8441,7 +8409,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_7</t>
+          <t>R02_BigGrassPoint_6</t>
         </is>
       </c>
       <c r="F139" s="8" t="n">
@@ -8449,22 +8417,22 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 9</t>
+          <t>B 2번 방 큰 풀 7</t>
         </is>
       </c>
       <c r="C140" s="8" t="n">
@@ -8477,7 +8445,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_9</t>
+          <t>R02_BigGrassPoint_7</t>
         </is>
       </c>
       <c r="F140" s="8" t="n">
@@ -8485,22 +8453,22 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="n">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 10</t>
+          <t>B 2번 방 큰 풀 9</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
@@ -8513,7 +8481,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_10</t>
+          <t>R02_BigGrassPoint_9</t>
         </is>
       </c>
       <c r="F141" s="8" t="n">
@@ -8521,22 +8489,22 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 큰 풀 11</t>
+          <t>B 2번 방 큰 풀 10</t>
         </is>
       </c>
       <c r="C142" s="8" t="n">
@@ -8549,7 +8517,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>R02_BigGrassPoint_11</t>
+          <t>R02_BigGrassPoint_10</t>
         </is>
       </c>
       <c r="F142" s="8" t="n">
@@ -8557,22 +8525,22 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="n">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 작은 풀 1</t>
+          <t>B 2번 방 큰 풀 11</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
@@ -8585,30 +8553,30 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>R02_SmallGrassPoint_1</t>
+          <t>R02_BigGrassPoint_11</t>
         </is>
       </c>
       <c r="F143" s="8" t="n">
-        <v>13054</v>
+        <v>13053</v>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="n">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 작은 풀 2</t>
+          <t>B 2번 방 작은 풀 1</t>
         </is>
       </c>
       <c r="C144" s="8" t="n">
@@ -8621,7 +8589,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>R02_SmallGrassPoint_2</t>
+          <t>R02_SmallGrassPoint_1</t>
         </is>
       </c>
       <c r="F144" s="8" t="n">
@@ -8629,10 +8597,154 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>장식</t>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="n">
+        <v>2234</v>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>B 2번 방 작은 풀 2</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>R02_SmallGrassPoint_2</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>13054</v>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_02 패키지로 대체 (A 소품 R02A_ObjectsPoint / B 소품 · 액자 R02B_ObjectsPoint 한 묶음). 장식</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n">
+        <v>2246</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>2번 방 천장 (A·B 공통)</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>R02_CeilingPoint</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>13072</v>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="n">
+        <v>2247</v>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>A 2번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>R02A_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="n">
+        <v>13073</v>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래 &gt; R02A. A 소품 전체가 프리팹 하나</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="n">
+        <v>2248</v>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>B 2번 방 소품 · 액자 묶음</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>R02B_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="n">
+        <v>13074</v>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래 &gt; R02B. 액자 · 풀 등 B 소품 전체가 프리팹 하나</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>A 7번 방 · 최종 방 (해결)</t>
+          <t>A 7번 방 · 최종 방 (해결, A·B 공통 구조 R07_Structure)</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>B 7번 방 · 최종 방 (해결)</t>
+          <t>B 7번 방 · 최종 방 (해결, A·B 공통 구조 R07_Structure)</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -2676,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 (문 모델 기준점). 문 프리팹 Door (모든 방 공통) / 이 앵커는 R01_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 (문 모델 기준점). 문 프리팹 Door (모든 방 공통) / 이 앵커는 R01_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래. 2번→3번 문틀 자리 (모델의 문 기준점과 같은 위치 · 회전). 문 프리팹 Door (모든 방 공통) / 이 앵커는 R02_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래. 2번→3번 문틀 자리 (모델의 문 기준점과 같은 위치 · 회전). 문 프리팹 Door (모든 방 공통) / 이 앵커는 R02_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 출구 문</t>
+          <t>3번 방 출구 문 (A·B 공통, 3번→4번)</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>R3A_DOOR_OUT</t>
+          <t>R03_DoorModelPoint</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>출구. 방 ExitRule대로 열림</t>
+          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래. 3번→4번 문틀 자리. 문 프리팹 Door (모든 방 공통) / 이 앵커는 R03_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -3113,11 +3113,11 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2012</v>
+        <v>2039</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 출구 문</t>
+          <t>B 3번 방 화살표 콘솔</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -3130,17 +3130,13 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>R3B_DOOR_OUT</t>
+          <t>R3B_CONSOLE</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13012</v>
+      </c>
+      <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3149,30 +3145,34 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>2039</v>
+        <v>2014</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 화살표 콘솔</t>
+          <t>4번 방 출구 문 (A·B 공통, 4번→5번)</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>R3B_CONSOLE</t>
+          <t>R04_DoorModelPoint</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>13012</v>
-      </c>
-      <c r="G17" s="8" t="n"/>
+        <v>13002</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래. 4번→5번 문틀 자리. 문 프리팹 Door (모든 방 공통) / 이 앵커는 R04_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
+        </is>
+      </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3181,11 +3181,11 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>2014</v>
+        <v>2042</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 출구 문</t>
+          <t>A 4번 방 5칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -3198,17 +3198,13 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>R4A_DOOR_OUT</t>
+          <t>R4A_LOCK</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13006</v>
+      </c>
+      <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3217,11 +3213,11 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>2016</v>
+        <v>2044</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 출구 문</t>
+          <t>B 4번 방 배선 콘솔</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -3234,15 +3230,15 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>R4B_DOOR_OUT</t>
+          <t>R4B_CONSOLE</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>13002</v>
+        <v>13013</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>출구. 방 ExitRule대로 열림</t>
+          <t>받침대 R4B_CONSOLE_STAND 위. 클릭하면 조작 화면이 열리고 뚜껑이 열려 안쪽 전선이 보임</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -3253,30 +3249,34 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2042</v>
+        <v>2018</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 5칸 다이얼 자물쇠</t>
+          <t>5번 방 출구 문 (A·B 공통, 5번→6번)</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>R4A_LOCK</t>
+          <t>R05_DoorModelPoint</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>13006</v>
-      </c>
-      <c r="G20" s="8" t="n"/>
+        <v>13002</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래. 5번→6번 문틀 자리. 문 프리팹 Door (모든 방 공통) / 이 앵커는 R05_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
+        </is>
+      </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3285,15 +3285,15 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2044</v>
+        <v>2051</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>B 4번 방 배선 콘솔</t>
+          <t>B 5번 방 4칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
@@ -3302,15 +3302,15 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>R4B_CONSOLE</t>
+          <t>R5B_LOCK</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>13013</v>
+        <v>13005</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>받침대 R4B_CONSOLE_STAND 위. 클릭하면 조작 화면이 열리고 뚜껑이 열려 안쪽 전선이 보임</t>
+          <t>C는 다이얼 2칸(십의 자리, 일의 자리)</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -3321,24 +3321,24 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>A 5번 방 출구 문</t>
+          <t>6번 방 출구 문 (A·B 공통, 6번→7번)</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>R5A_DOOR_OUT</t>
+          <t>R06_DoorModelPoint</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>출구. 방 ExitRule대로 열림</t>
+          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래. 6번→7번 문틀 자리. 문 프리팹 Door (모든 방 공통) / 이 앵커는 R06_DoorPoint(방 연결점, 문턱 중앙 바닥, Z+ = 방 바깥쪽, 코드 전용·DataTable 행 없음)의 자식. 문 모델 회전과 바닥 위 1.15 m 높이를 이 앵커가 가짐</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -3357,32 +3357,32 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2020</v>
+        <v>2054</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 출구 문</t>
+          <t>A 6번 방 5칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>R5B_DOOR_OUT</t>
+          <t>R6A_LOCK</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>13002</v>
+        <v>13006</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>출구. 방 ExitRule대로 열림</t>
+          <t>다이얼마다 정답 글자를 포함한 9자 고정 / A 소품 묶음에 있던 파란 자물쇠 모델은 지움 (받침대는 남김). 자리는 받침대 위 방 기준 약 (-78.1, 0.94, 8.6). 앵커 · 프리팹 미정</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -3393,32 +3393,32 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2051</v>
+        <v>2026</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 4칸 다이얼 자물쇠</t>
+          <t>7번 방 탈출구 문 (A·B 공통, 엔딩)</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>R5B_LOCK</t>
+          <t>R07_DoorModelPoint</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>C는 다이얼 2칸(십의 자리, 일의 자리)</t>
+          <t>방 프리팹 R07_Structure &gt; R07_Points 아래. 탈출구 문틀 자리. 문 프리팹 Door (모든 방 공통) / 이 앵커는 R07_EndingPoint(탈출구 문턱 중앙 바닥, Z+ = 방 바깥쪽, 엔딩 영상 GAME_CONFIG 16011 재생 지점, 코드 전용·DataTable 행 없음)의 자식. 방 ExitRule(BothSolved)대로 열림</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -3429,15 +3429,15 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>2022</v>
+        <v>2071</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 출구 문</t>
+          <t>A 7번 방 6칸 색 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
@@ -3446,17 +3446,13 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>R6A_DOOR_OUT</t>
+          <t>R7A_LOCK</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13007</v>
+      </c>
+      <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3465,15 +3461,15 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>2024</v>
+        <v>2073</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>B 6번 방 출구 문</t>
+          <t>B 7번 방 6칸 색 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
@@ -3482,190 +3478,14 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>R6B_DOOR_OUT</t>
+          <t>R7B_LOCK</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
+        <v>13007</v>
+      </c>
+      <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>2054</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>A 6번 방 5칸 다이얼 자물쇠</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>R6A_LOCK</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>13006</v>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>다이얼마다 정답 글자를 포함한 9자 고정</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>A 7번 방 출구 문</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>R7A_DOOR_OUT</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>B 7번 방 출구 문</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>R7B_DOOR_OUT</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>13002</v>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>출구. 방 ExitRule대로 열림</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>2071</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>A 7번 방 6칸 색 다이얼 자물쇠</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>R7A_LOCK</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>13007</v>
-      </c>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>2073</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>B 7번 방 6칸 색 다이얼 자물쇠</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>R7B_LOCK</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>13007</v>
-      </c>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3699,7 +3519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -4165,7 +3985,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 R01_Player (A · B가 같은 자리에서 시작, 사용자 결정). 프리팹 13001 경로는 아직 예시라 실제 플레이어 시작 프리팹이 필요함</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 R01_Player (A · B가 같은 자리에서 시작, 사용자 결정). 프리팹 13001 경로는 아직 예시라 실제 플레이어 시작 프리팹이 필요함</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -4201,7 +4021,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -4237,7 +4057,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: 기본 방(Room_01_Final)에 천장 포함 · 꺼둠</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: 기본 방(Room_01_Final)에 천장 포함 · 꺼둠</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -4309,7 +4129,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문 / R01_v3: 기본 방(Room_01_Final)에 dver' 포함 · 꺼둠</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문 / R01_v3: 기본 방(Room_01_Final)에 dver' 포함 · 꺼둠</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -4345,7 +4165,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -4381,7 +4201,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; Room_01_A_Structure &gt; R01_Points &gt; R01A 아래. 방 원점 (0,0,0), 회전 없음: Room_01_Final 1 안 모델들이 방 기준 절대 위치로 저장돼 있어 원점에 두면 제자리에 놓임. B는 생성 안 함</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01A 아래. 방 원점 (0,0,0), 회전 없음: Room_01_Final 1 안 모델들이 방 기준 절대 위치로 저장돼 있어 원점에 두면 제자리에 놓임. B는 생성 안 함</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -5489,12 +5309,12 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_01_RIGHT</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5345,12 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_02_UP</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5561,12 +5381,12 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_03_LEFT</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5417,12 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_04_DOWN</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5453,12 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_05_RIGHT</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5489,12 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_06_DOWN</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5705,12 +5525,12 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_07_LEFT</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5741,12 +5561,12 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_08_UP</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5777,12 +5597,12 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_09_RIGHT</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5813,12 +5633,12 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
+          <t>SILENT_Room_03 패키지로 대체 (A 소품 R03A_ObjectsPoint / B 소품 R03B_ObjectsPoint 한 묶음). 모델러 파일 이름 PZ_R3_A_Clue_10_DOWN</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5847,10 +5667,14 @@
       <c r="F63" s="8" t="n">
         <v>13003</v>
       </c>
-      <c r="G63" s="8" t="n"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5913,12 +5737,12 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 아래 받침대, 40×30cm, 높이 90cm</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5949,12 +5773,12 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5809,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6021,12 +5845,12 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6057,12 +5881,12 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6093,12 +5917,12 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6129,12 +5953,12 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6165,12 +5989,12 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6025,12 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6237,12 +6061,12 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6273,12 +6097,12 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>배선 콘솔 안 단자에 연결</t>
+          <t>SILENT_Room_04 패키지로 대체 (A 소품 R04A_ObjectsPoint / B 소품 R04B_ObjectsPoint 한 묶음). 배선 콘솔 안 단자에 연결</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6307,10 +6131,14 @@
       <c r="F76" s="8" t="n">
         <v>13003</v>
       </c>
-      <c r="G76" s="8" t="n"/>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6339,10 +6167,14 @@
       <c r="F77" s="8" t="n">
         <v>13016</v>
       </c>
-      <c r="G77" s="8" t="n"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6371,10 +6203,14 @@
       <c r="F78" s="8" t="n">
         <v>13004</v>
       </c>
-      <c r="G78" s="8" t="n"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6435,10 +6271,14 @@
       <c r="F80" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G80" s="8" t="n"/>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6467,10 +6307,14 @@
       <c r="F81" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G81" s="8" t="n"/>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6499,10 +6343,14 @@
       <c r="F82" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G82" s="8" t="n"/>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6531,10 +6379,14 @@
       <c r="F83" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G83" s="8" t="n"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6563,10 +6415,14 @@
       <c r="F84" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G84" s="8" t="n"/>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6595,10 +6451,14 @@
       <c r="F85" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G85" s="8" t="n"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6627,10 +6487,14 @@
       <c r="F86" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G86" s="8" t="n"/>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6659,10 +6523,14 @@
       <c r="F87" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G87" s="8" t="n"/>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6691,10 +6559,14 @@
       <c r="F88" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G88" s="8" t="n"/>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6723,10 +6595,14 @@
       <c r="F89" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G89" s="8" t="n"/>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6755,10 +6631,14 @@
       <c r="F90" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G90" s="8" t="n"/>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6787,10 +6667,14 @@
       <c r="F91" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G91" s="8" t="n"/>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6819,10 +6703,14 @@
       <c r="F92" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G92" s="8" t="n"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6851,10 +6739,14 @@
       <c r="F93" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G93" s="8" t="n"/>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6883,10 +6775,14 @@
       <c r="F94" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G94" s="8" t="n"/>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6915,10 +6811,14 @@
       <c r="F95" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G95" s="8" t="n"/>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6947,10 +6847,14 @@
       <c r="F96" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G96" s="8" t="n"/>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6979,10 +6883,14 @@
       <c r="F97" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G97" s="8" t="n"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7011,10 +6919,14 @@
       <c r="F98" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G98" s="8" t="n"/>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7043,10 +6955,14 @@
       <c r="F99" s="8" t="n">
         <v>13014</v>
       </c>
-      <c r="G99" s="8" t="n"/>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILENT_Room_05 패키지로 대체 (A 소품 R05A_ObjectsPoint / B 소품 R05B_ObjectsPoint 한 묶음). </t>
+        </is>
+      </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7075,10 +6991,14 @@
       <c r="F100" s="8" t="n">
         <v>13004</v>
       </c>
-      <c r="G100" s="8" t="n"/>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (A 소품 R06A_ObjectsPoint 한 묶음 안에 포함)</t>
+        </is>
+      </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7107,10 +7027,14 @@
       <c r="F101" s="8" t="n">
         <v>13008</v>
       </c>
-      <c r="G101" s="8" t="n"/>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (A 소품 R06A_ObjectsPoint 한 묶음 안에 포함)</t>
+        </is>
+      </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7139,10 +7063,14 @@
       <c r="F102" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G102" s="8" t="n"/>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7171,10 +7099,14 @@
       <c r="F103" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G103" s="8" t="n"/>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7203,10 +7135,14 @@
       <c r="F104" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G104" s="8" t="n"/>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7235,10 +7171,14 @@
       <c r="F105" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G105" s="8" t="n"/>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7267,10 +7207,14 @@
       <c r="F106" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G106" s="8" t="n"/>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7299,10 +7243,14 @@
       <c r="F107" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G107" s="8" t="n"/>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7331,10 +7279,14 @@
       <c r="F108" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G108" s="8" t="n"/>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7363,10 +7315,14 @@
       <c r="F109" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G109" s="8" t="n"/>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7395,10 +7351,14 @@
       <c r="F110" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G110" s="8" t="n"/>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7427,10 +7387,14 @@
       <c r="F111" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G111" s="8" t="n"/>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7459,10 +7423,14 @@
       <c r="F112" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G112" s="8" t="n"/>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7491,10 +7459,14 @@
       <c r="F113" s="8" t="n">
         <v>13017</v>
       </c>
-      <c r="G113" s="8" t="n"/>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>SILENT_Room_06 패키지로 대체 (B 소품 R06B_ObjectsPoint 한 묶음 안에 TV 12대 모델 포함, 화면 글자 자리는 프리팹 안 PZ_R6_B_TV_01~12). TV 시트 값은 유지</t>
+        </is>
+      </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8641,7 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
@@ -8705,7 +8677,7 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래 &gt; R02A. A 소품 전체가 프리팹 하나</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래 &gt; R02A. A 소품 전체가 프리팹 하나</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
@@ -8741,10 +8713,478 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_02_Structure &gt; Room_02_B_Structure &gt; R02_Points 아래 &gt; R02B. 액자 · 풀 등 B 소품 전체가 프리팹 하나</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래 &gt; R02B. 액자 · 풀 등 B 소품 전체가 프리팹 하나</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>3번 방 천장 (A·B 공통)</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>R03_CeilingPoint</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="n">
+        <v>13076</v>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래. 지금은 천장이 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.002를 지울 때 Y로</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="n">
+        <v>2251</v>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>A 3번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>R03A_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="n">
+        <v>13077</v>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래 &gt; R03A. A 소품 전체(조명 · 벽 무늬 · 문틀)가 프리팹 하나. B 묶음과 같은 자리</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="n">
+        <v>2252</v>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>B 3번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>R03B_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="n">
+        <v>13078</v>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래 &gt; R03B. B 소품 전체가 프리팹 하나. A 묶음과 같은 자리 (B 모델은 원래 z -6.5에 있어 프리팹 안에서 +13 m 옮겨 A 방 자리에 맞춤)</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="n">
+        <v>2253</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>4번 방 천장 (A·B 공통)</t>
+        </is>
+      </c>
+      <c r="C152" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>R04_CeilingPoint</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="n">
+        <v>13079</v>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래. 지금은 천장 Ceiling.003이 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.003을 지울 때 Y로</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="n">
+        <v>2254</v>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>A 4번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>R04A_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="n">
+        <v>13080</v>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래 &gt; R04A. A 소품 전체가 메시 하나인 프리팹. 위치 · 회전은 모델 기준점 그대로 (바닥 위 3.765 m, X -90). B 묶음과 같은 자리</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="n">
+        <v>2255</v>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>B 4번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>R04B_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="n">
+        <v>13081</v>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래 &gt; R04B. B 소품 전체가 메시 하나인 프리팹. A 묶음과 같은 자리 (B 모델은 원래 z -6.5 옆방 자리지만 기준점이 A와 같은 상대 위치라 같은 앵커에 맞음)</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="n">
+        <v>2256</v>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>5번 방 천장 (A·B 공통)</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>R05_CeilingPoint</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="n">
+        <v>13082</v>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래. 지금은 천장 Ceiling.004가 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.004를 지울 때 Y로</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="n">
+        <v>2257</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>A 5번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>R05A_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="n">
+        <v>13083</v>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래 &gt; R05A. A 소품 전체가 프리팹 하나 (빈 루트 = 방 기준점, 안에 메시 Room_05_A_Objects). B 묶음과 같은 자리</t>
+        </is>
+      </c>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="n">
+        <v>2258</v>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>B 5번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>R05B_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="n">
+        <v>13084</v>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래 &gt; R05B. B 소품 전체가 프리팹 하나 (빈 루트 = 방 기준점, 안에 메시 Room_05_B_Objects를 +13 m 옮겨 A 방 자리에 맞춤). A 묶음과 같은 자리</t>
+        </is>
+      </c>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="n">
+        <v>2259</v>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>6번 방 천장 (A·B 공통)</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>R06_CeilingPoint</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="n">
+        <v>13085</v>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래. 지금은 천장 Ceiling.005가 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.005를 지울 때 Y로</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="n">
+        <v>2260</v>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>A 6번 방 소품 묶음</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>R06A_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="n">
+        <v>13086</v>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래 &gt; R06A. A 소품 전체가 메시 하나인 프리팹. 위치 · 회전은 모델 기준점 그대로 (방 중앙 바닥, X -90). B 묶음과 같은 자리</t>
+        </is>
+      </c>
+      <c r="H159" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="n">
+        <v>2261</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>B 6번 방 소품 · TV 묶음</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>R06B_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="n">
+        <v>13087</v>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래 &gt; R06B. B 소품과 TV 12대가 메시 하나인 프리팹 (TV 화면 자리 PZ_R6_B_TV_01~12 포함). A 묶음과 같은 자리 (B 모델은 원래 z -6.5 옆방 자리지만 기준점이 A와 같은 상대 위치라 같은 앵커에 맞음)</t>
+        </is>
+      </c>
+      <c r="H160" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="n">
+        <v>2262</v>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>7번 방 소품 묶음 (A·B 공통)</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t>R07_ObjectsPoint</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="n">
+        <v>13088</v>
+      </c>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 R07_Structure &gt; R07_Points 아래. 걸레받이 · 천장 조명 · 문 옆 판이 메시 하나인 프리팹. 방 중앙 바닥 (-83, 0, 6.5), 회전 없음</t>
+        </is>
+      </c>
+      <c r="H161" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -2833,7 +2833,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>B 1번 방 다이얼 테이블 (자물쇠 자리)</t>
+          <t>B 1번 방 4칸 다이얼 자물쇠</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -2846,20 +2846,20 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>R01_Dial_table_Anchor</t>
+          <t>R01B_LockPoint</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>13045</v>
+        <v>13089</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>TestScene에 아직 앵커 없음 (모델러 작업 중). 앵커가 생기면 그 Point 이름으로 AnchorID를 바꾸고 Active Y. LOCK 2030 · PUZZLE 5001 InputAnchor가 이 행을 가리킴</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01B 아래. 출구 문 옆 벽, 바닥에서 1.14 m. 다이얼 1~9. LOCK 2030 · PUZZLE 5001 InputAnchor가 이 행을 가리킴. 예전 다이얼 테이블(13045)과 다이얼 2201~2204는 안 씀</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3062,13 +3062,17 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>R2A_LOCK</t>
+          <t>R02A_LockPoint</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
         <v>13005</v>
       </c>
-      <c r="G14" s="8" t="n"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Points &gt; R02A 아래. 출구 문 옆 벽, 바닥에서 1.15 m</t>
+        </is>
+      </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3130,13 +3134,17 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>R3B_CONSOLE</t>
+          <t>R03B_ConsolePoint</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
         <v>13012</v>
       </c>
-      <c r="G16" s="8" t="n"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Points &gt; R03B 아래. 출구 문 옆 벽, 바닥에서 1.11 m</t>
+        </is>
+      </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3198,13 +3206,17 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>R4A_LOCK</t>
+          <t>R04A_LockPoint</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
         <v>13006</v>
       </c>
-      <c r="G18" s="8" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; R04_Points &gt; R04A 아래. 출구 문 옆 벽, 바닥에서 1.55 m. 다이얼 1~9</t>
+        </is>
+      </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3230,7 +3242,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>R4B_CONSOLE</t>
+          <t>R04B_ConsolePoint</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
@@ -3238,7 +3250,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>받침대 R4B_CONSOLE_STAND 위. 클릭하면 조작 화면이 열리고 뚜껑이 열려 안쪽 전선이 보임</t>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; R04_Points &gt; R04B 아래. 방 가운데 바닥 (뚜껑 열린 배선 콘솔 모델, 크기 2배). 받침대 따로 없음</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -3302,15 +3314,15 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>R5B_LOCK</t>
+          <t>R05B_LockPoint</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>13005</v>
+        <v>13090</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>C는 다이얼 2칸(십의 자리, 일의 자리)</t>
+          <t>방 프리팹 SILENT_Room_05_Structure &gt; R05_Points &gt; R05B 아래. 출구 문 옆 벽, 바닥에서 1.12 m. 다이얼 0~9</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -3374,15 +3386,15 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>R6A_LOCK</t>
+          <t>R06A_LockPoint</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>13006</v>
+        <v>13091</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>다이얼마다 정답 글자를 포함한 9자 고정 / A 소품 묶음에 있던 파란 자물쇠 모델은 지움 (받침대는 남김). 자리는 받침대 위 방 기준 약 (-78.1, 0.94, 8.6). 앵커 · 프리팹 미정</t>
+          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; R06_Points &gt; R06A 아래. A 소품 묶음의 받침대 위, 바닥에서 1.04 m. 다이얼마다 정답 글자를 포함한 9자 고정</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -3446,13 +3458,17 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>R7A_LOCK</t>
+          <t>R07A_LockPoint</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
         <v>13007</v>
       </c>
-      <c r="G25" s="8" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 R07_Structure &gt; R07_Points 바로 아래. 출구(엔딩) 벽, 바닥에서 1.16 m. 안내 글자 L I S T E N. B 앵커 2073과 같은 자리</t>
+        </is>
+      </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3478,13 +3494,17 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>R7B_LOCK</t>
+          <t>R07B_LockPoint</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13007</v>
-      </c>
-      <c r="G26" s="8" t="n"/>
+        <v>13092</v>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>방 프리팹 R07_Structure &gt; R07_Points 바로 아래. 출구(엔딩) 벽, 바닥에서 1.16 m. 안내 글자 S I L E N T (B용 프리팹 R07B_Lock). A 앵커 2071과 같은 자리</t>
+        </is>
+      </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3905,7 +3925,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>R01_LEDPanelPoint</t>
+          <t>R01B_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
@@ -3913,7 +3933,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>B만 출력. COLOR_LETTER 7001 SignAnchor가 이 행을 가리킴</t>
+          <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01B 아래. 출구 문 위, 출구 문 위 바닥에서 2.73 m, 출구 벽 안쪽 면. 방 안쪽을 봄. COLOR_LETTER 7001 SignAnchor가 이 행을 가리킴</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -4265,13 +4285,17 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>R2A_SIGN</t>
+          <t>R02A_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G24" s="8" t="n"/>
+        <v>13043</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_02_Structure &gt; R02_Points &gt; R02A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7002 SignAnchor가 이 행을 가리킴</t>
+        </is>
+      </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5269,13 +5293,17 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>R3B_SIGN</t>
+          <t>R03B_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G52" s="8" t="n"/>
+        <v>13043</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_03_Structure &gt; R03_Points &gt; R03B 아래. 출구 문 위, B 소품 묶음 안 PZ_R3_B_RewardDisplay 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7003 SignAnchor가 이 행을 가리킴</t>
+        </is>
+      </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5697,13 +5725,17 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>R4A_SIGN</t>
+          <t>R04A_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G64" s="8" t="n"/>
+        <v>13043</v>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_04_Structure &gt; R04_Points &gt; R04A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7004 SignAnchor가 이 행을 가리킴</t>
+        </is>
+      </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6233,13 +6265,17 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>R5B_SIGN</t>
+          <t>R05B_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F79" s="8" t="n">
-        <v>13008</v>
-      </c>
-      <c r="G79" s="8" t="n"/>
+        <v>13043</v>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_05_Structure &gt; R05_Points &gt; R05B 아래. 출구 문 위, B 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7005 SignAnchor가 이 행을 가리킴</t>
+        </is>
+      </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7021,20 +7057,20 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>R6A_SIGN</t>
+          <t>R06A_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F101" s="8" t="n">
-        <v>13008</v>
+        <v>13043</v>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>SILENT_Room_06 패키지로 대체 (A 소품 R06A_ObjectsPoint 한 묶음 안에 포함)</t>
+          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_06_A_Structure &gt; R06_Points &gt; R06A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7006 SignAnchor가 이 행을 가리킴</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -7495,10 +7531,14 @@
       <c r="F114" s="8" t="n">
         <v>13004</v>
       </c>
-      <c r="G114" s="8" t="n"/>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>7번 방 자물쇠는 벽에 붙어 있어 받침대 없음</t>
+        </is>
+      </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7527,10 +7567,14 @@
       <c r="F115" s="8" t="n">
         <v>13004</v>
       </c>
-      <c r="G115" s="8" t="n"/>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>7번 방 자물쇠는 벽에 붙어 있어 받침대 없음</t>
+        </is>
+      </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>

--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="140" customWidth="1" style="10" min="1" max="1"/>
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>파일 6개, 시트 23개. 시트 하나 = CSV 하나(시트 이름.csv, UTF-8). _README · _COLUMNS 시트는 설명용이라 내보내지 않습니다.</t>
+          <t>파일 6개, 시트 16개. 시트 하나 = CSV 하나(시트 이름.csv, UTF-8). _README · _COLUMNS 시트는 설명용이라 내보내지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx: LOCK, CONSOLE, CARD, FRAME, ARROW, WIRE, FORMULA, PAPER, TV</t>
+          <t>SILENT_Object_Datatable.xlsx: LOCK, CONSOLE</t>
         </is>
       </c>
     </row>
@@ -673,184 +673,164 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  │    └ CARD · FRAME · ARROW · WIRE · FORMULA · PAPER · TV (앵커의 값, AnchorRef)</t>
+          <t xml:space="preserve">  └ PUZZLE (퍼즐, SolverRoom · ClueRoom, 입력 장치 InputAnchor)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ PUZZLE (퍼즐, SolverRoom · ClueRoom, 입력 장치 InputAnchor)</t>
+          <t xml:space="preserve">       ├ PUZZLE_SLOT (정답 칸, PuzzleID)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       ├ PUZZLE_SLOT (정답 칸, PuzzleID)</t>
+          <t xml:space="preserve">       └ COLOR_LETTER (풀리면 보여 줄 색 글자, PuzzleID, 표시판 SignAnchor)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └ COLOR_LETTER (풀리면 보여 줄 색 글자, PuzzleID, 표시판 SignAnchor)</t>
+          <t>라이브러리: PREFAB ← COMPONENT (Components), SOUND ← SOUND_LINK (SoundID), GAME_CONFIG → CHARACTER_STAT (16010)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>라이브러리: PREFAB ← COMPONENT (Components), SOUND ← SOUND_LINK (SoundID), GAME_CONFIG → CHARACTER_STAT (16010)</t>
+          <t>전체 시트 목록, 부모, 읽는 순서: Settings 파일의 REGISTRY</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>전체 시트 목록, 부모, 읽는 순서: Settings 파일의 REGISTRY</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>공통 규칙</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>공통 규칙</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1~5행: 1행 그 시트만의 규칙, 2행 기능, 3행 역할, 4행 의도, 5행 비고(코드가 읽지 않는 열). 6행 열 이름, 7행부터 데이터. CSV 리더는 앞 5줄을 건너뜀</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1~5행: 1행 그 시트만의 규칙, 2행 기능, 3행 역할, 4행 의도, 5행 비고(코드가 읽지 않는 열). 6행 열 이름, 7행부터 데이터. CSV 리더는 앞 5줄을 건너뜀</t>
+          <t>1열 ID: 숫자, 시트 구간 안에서 차례로. 지운 번호는 다시 쓰지 않음. Object 파일 시트의 1열 AnchorRef는 새 번호가 아니라 앵커 ID(두 앵커 시트가 2001~ 구간을 함께 써서 번호가 겹치지 않음.)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="27.75" customHeight="1" s="10">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1열 ID: 숫자, 시트 구간 안에서 차례로. 지운 번호는 다시 쓰지 않음. Object 파일 시트의 1열 AnchorRef는 새 번호가 아니라 앵커 ID(두 앵커 시트가 2001~ 구간을 함께 써서 번호가 겹치지 않음. 카드는 여러 장이 한 앵커라 CARD만 자기 ID 3001~)</t>
+          <t>2열 Name: 한국어 설명. 겹쳐도 되고 코드가 읽지 않음. 겹치면 안 되는 문자열은 두 앵커 시트의 AnchorID(Unity 앵커 이름) 하나</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2열 Name: 한국어 설명. 겹쳐도 되고 코드가 읽지 않음. 겹치면 안 되는 문자열은 두 앵커 시트의 AnchorID(Unity 앵커 이름) 하나</t>
+          <t>참조: 다른 시트는 숫자 ID로만 가리킴. 여러 개면 | 로 구분</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>참조: 다른 시트는 숫자 ID로만 가리킴. 여러 개면 | 로 구분</t>
+          <t>코드가 읽는 단어 값(색, 방향, 기호, 유형)은 아래 정해진 영어 단어로 씀</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>코드가 읽는 단어 값(색, 방향, 기호, 유형)은 아래 정해진 영어 단어로 씀</t>
+          <t>Active = N인 행은 읽지 않음. 단위: 거리 m, 시간 ms(밀리초, 1000 = 1초, 정수). 좌표는 DataTable에 없음(앵커 자리는 Unity 방 프리팹에서 정함)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Active = N인 행은 읽지 않음. 단위: 거리 m, 시간 ms(밀리초, 1000 = 1초, 정수). 좌표는 DataTable에 없음(앵커 자리는 Unity 방 프리팹에서 정함)</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>정해진 단어</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>정해진 단어</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Colour: Red, Green, Blue, Gray, Black, Orange, Yellow, SkyBlue, Pink, Purple, Crimson, White, Teal, Navy (글자 색 6개의 코드는 아트 01)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Colour: Red, Green, Blue, Gray, Black, Orange, Yellow, SkyBlue, Pink, Purple, Crimson, White, Teal, Navy (글자 색 6개의 코드는 아트 01)</t>
+          <t>Symbol: BlackDiamond ◆, WhiteDiamond ◇, BlackSpade ♠, WhiteSpade ♤, BlackHeart ♥, WhiteHeart ♡, Star ★, Heart (빨간 하트 그림), Spade (검은 스페이드 그림), None</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Symbol: BlackDiamond ◆, WhiteDiamond ◇, BlackSpade ♠, WhiteSpade ♤, BlackHeart ♥, WhiteHeart ♡, Star ★, Heart (빨간 하트 그림), Spade (검은 스페이드 그림), None</t>
+          <t>Direction: Up, Down, Left, Right / Wall: North, South</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Direction: Up, Down, Left, Right / Wall: North, South</t>
+          <t>Role: Solver, Clue / ExitRule: SolvedEach, BothSolved</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Role: Solver, Clue / ExitRule: SolvedEach, BothSolved</t>
+          <t>Type (PUZZLE): CardLetter, FrameCount, ArrowSequence, WireRank, TwistedFormula, TVLetter, ColourWord</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Type (PUZZLE): CardLetter, FrameCount, ArrowSequence, WireRank, TwistedFormula, TVLetter, ColourWord</t>
+          <t>DialFace (LOCK): Number1_9, Number0_9, Letter9, Color6 / DisplayFace: Letter, Color, Number, LetterWindow</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DecoyType (CARD): None, LetterLetter, NumberNumber, SymbolZero, SymbolOne, SymbolTwo, SymbolThree, SymbolFour, IconIcon</t>
+          <t>Trigger (SOUND_LINK): OnStep, OnInteract, OnCloseUpOpen, OnCloseUpClose, OnDialTurn, OnConfirm, OnButton, OnClear, OnSpawn, OnDoorOpen, OnDoorLocked, OnSolved, OnLetterShow, OnWrong, OnInputUnlock, OnRoomEnter, OnRadioRxStart, OnRadioRxEnd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Category (FORMULA): Definition, Basic, Linear, Quadratic, Cubic, School, Discrete</t>
+          <t>Category (SOUND): Footstep, Interact, ObjectLoop, Door, PuzzleSolved, PuzzleWrong, Ambient, Radio / Space: 2D, 3D / Bus: SFX, Ambient, UI, Radio</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DialFace (LOCK): Number1_9, Number0_9, Letter9, Color6 / DisplayFace: Letter, Color, Number, LetterWindow</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="27.75" customHeight="1" s="10">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Trigger (SOUND_LINK): OnStep, OnInteract, OnCloseUpOpen, OnCloseUpClose, OnDialTurn, OnConfirm, OnButton, OnClear, OnSpawn, OnDoorOpen, OnDoorLocked, OnSolved, OnLetterShow, OnWrong, OnInputUnlock, OnRoomEnter, OnRadioRxStart, OnRadioRxEnd</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Category (SOUND): Footstep, Interact, ObjectLoop, Door, PuzzleSolved, PuzzleWrong, Ambient, Radio / Space: 2D, 3D / Bus: SFX, Ambient, UI, Radio</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Y / N: Active, IsAnswer (정답에 쓰이는 것 = Y: CARD, FRAME, ARROW, WIRE, FORMULA, PAPER, TV), Flip, Loop, Required</t>
-        </is>
-      </c>
-    </row>
+          <t>Y / N: Active, Flip, Loop, Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="27.75" customHeight="1" s="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3395,7 +3375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -3440,7 +3420,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>ROOM_A · ROOM_B의 자식(RoomNo + PlayerType으로 방 행을 찾음), CARD · FRAME · ARROW · WIRE · FORMULA · PAPER · TV 값 시트와 COLOR_LETTER.SignAnchor가 가리킴. 기획이 PrefabID를 정하고, 작업자가 Unity에 앵커를 놓고, 개발이 스폰 코드를 쓴다.</t>
+          <t>ROOM_A · ROOM_B의 자식(RoomNo + PlayerType으로 방 행을 찾음), COLOR_LETTER.SignAnchor가 가리킴. 기획이 PrefabID를 정하고, 작업자가 Unity에 앵커를 놓고, 개발이 스폰 코드를 쓴다.</t>
         </is>
       </c>
     </row>
@@ -3584,11 +3564,11 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>2237</v>
+        <v>2249</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>A 1번 방 바닥 카드</t>
+          <t>A 1번 방 소품 (서랍장 · 바닥 카드, Room_01_Final 1)</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -3601,178 +3581,178 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>R01A_CardsPoint</t>
+          <t>R01A_PropsPoint</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>13067</v>
+        <v>13075</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01A 아래 (A만 스폰). SILENT_Room_01_Final 안 Room_01_A_Cards 위치 · 회전 그대로. CARD 3001~3050이 가리킴 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
+          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01A 아래. 방 원점 (0,0,0), 회전 없음: Room_01_Final 1 안 모델들이 방 기준 절대 위치로 저장돼 있어 원점에 두면 제자리에 놓임. B는 생성 안 함</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>2238</v>
+        <v>2035</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>1번 방 천장 (A·B 공통)</t>
+          <t>A 2번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>R01_CeilingPoint</t>
+          <t>R02A_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>13068</v>
+        <v>13043</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: 기본 방(Room_01_Final)에 천장 포함 · 꺼둠</t>
+          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_02_Structure &gt; R02_Points &gt; R02A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7002 SignAnchor가 이 행을 가리킴</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>2239</v>
+        <v>2040</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>1번 방 바닥·벽 (A·B 공통)</t>
+          <t>B 3번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>R01_StructurePoint</t>
+          <t>R03B_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>13069</v>
+        <v>13043</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>바닥·벽은 방 프리팹(Room_01_Final, PREFAB 13020/13027) 자체라 따로 스폰하지 않음. 앵커 오브젝트는 프리팹 안에 남아 있음</t>
+          <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_03_Structure &gt; R03_Points &gt; R03B 아래. 출구 문 위, B 소품 묶음 안 PZ_R3_B_RewardDisplay 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7003 SignAnchor가 이 행을 가리킴</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>2240</v>
+        <v>2043</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>1번 방 문 막기용 문 dver' (A·B 공통)</t>
+          <t>A 4번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>R01_DverPoint</t>
+          <t>R04A_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>13070</v>
+        <v>13043</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로. 1번 방에만 있음. 열리지 않는 문 / R01_v3: 기본 방(Room_01_Final)에 dver' 포함 · 꺼둠</t>
+          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_04_Structure &gt; R04_Points &gt; R04A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7004 SignAnchor가 이 행을 가리킴</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>2241</v>
+        <v>2052</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>1번 방 서랍장 (A·B 공통)</t>
+          <t>B 5번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>R01_DrawerPoint</t>
+          <t>R05B_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>13071</v>
+        <v>13043</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points 아래 공용 앵커 (A · B가 같은 앵커 하나를 씀). SILENT_Room_01_Final 안 같은 오브젝트의 위치 · 회전 그대로 / R01_v3: Room_01_Final 1(2249)로 옮김 · 꺼둠</t>
+          <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_05_Structure &gt; R05_Points &gt; R05B 아래. 출구 문 위, B 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7005 SignAnchor가 이 행을 가리킴</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>2249</v>
+        <v>2055</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>A 1번 방 소품 (서랍장 · 바닥 카드, Room_01_Final 1)</t>
+          <t>A 6번 방 글자 표시판</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
@@ -3781,15 +3761,15 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>R01A_PropsPoint</t>
+          <t>R06A_LEDPanelPoint</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>13075</v>
+        <v>13043</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01A 아래. 방 원점 (0,0,0), 회전 없음: Room_01_Final 1 안 모델들이 방 기준 절대 위치로 저장돼 있어 원점에 두면 제자리에 놓임. B는 생성 안 함</t>
+          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_06_A_Structure &gt; R06_Points &gt; R06A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7006 SignAnchor가 이 행을 가리킴</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -3800,11 +3780,11 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>2035</v>
+        <v>2246</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 글자 표시판</t>
+          <t>2번 방 천장 (A·B 공통)</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -3812,20 +3792,20 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>R02A_LEDPanelPoint</t>
+          <t>R02_CeilingPoint</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>13043</v>
+        <v>13072</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_02_Structure &gt; R02_Points &gt; R02A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7002 SignAnchor가 이 행을 가리킴</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -3836,32 +3816,32 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2040</v>
+        <v>2247</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 글자 표시판</t>
+          <t>A 2번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>R03B_LEDPanelPoint</t>
+          <t>R02A_ObjectsPoint</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>13043</v>
+        <v>13073</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_03_Structure &gt; R03_Points &gt; R03B 아래. 출구 문 위, B 소품 묶음 안 PZ_R3_B_RewardDisplay 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7003 SignAnchor가 이 행을 가리킴</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래 &gt; R02A. A 소품 전체가 프리팹 하나</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -3872,32 +3852,32 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>2043</v>
+        <v>2248</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>A 4번 방 글자 표시판</t>
+          <t>B 2번 방 소품 · 액자 묶음</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>R04A_LEDPanelPoint</t>
+          <t>R02B_ObjectsPoint</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>13043</v>
+        <v>13074</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_04_Structure &gt; R04_Points &gt; R04A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7004 SignAnchor가 이 행을 가리킴</t>
+          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래 &gt; R02B. 액자 · 풀 등 B 소품 전체가 프리팹 하나</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -3908,32 +3888,32 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>2052</v>
+        <v>2251</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>B 5번 방 글자 표시판</t>
+          <t>A 3번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>R05B_LEDPanelPoint</t>
+          <t>R03A_ObjectsPoint</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>13043</v>
+        <v>13077</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_05_Structure &gt; R05_Points &gt; R05B 아래. 출구 문 위, B 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7005 SignAnchor가 이 행을 가리킴</t>
+          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래 &gt; R03A. A 소품 전체(조명 · 벽 무늬 · 문틀)가 프리팹 하나. B 묶음과 같은 자리</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -3944,32 +3924,32 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>2055</v>
+        <v>2252</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>A 6번 방 글자 표시판</t>
+          <t>B 3번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>R06A_LEDPanelPoint</t>
+          <t>R03B_ObjectsPoint</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>13043</v>
+        <v>13078</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_06_A_Structure &gt; R06_Points &gt; R06A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7006 SignAnchor가 이 행을 가리킴</t>
+          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래 &gt; R03B. B 소품 전체가 프리팹 하나. A 묶음과 같은 자리 (B 모델은 원래 z -6.5에 있어 프리팹 안에서 +13 m 옮겨 A 방 자리에 맞춤)</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -3980,32 +3960,32 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2246</v>
+        <v>2254</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>2번 방 천장 (A·B 공통)</t>
+          <t>A 4번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>R02_CeilingPoint</t>
+          <t>R04A_ObjectsPoint</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>13072</v>
+        <v>13080</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래</t>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래 &gt; R04A. A 소품 전체가 메시 하나인 프리팹. 위치 · 회전은 모델 기준점 그대로 (바닥 위 3.765 m, X -90). B 묶음과 같은 자리</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -4016,32 +3996,32 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2247</v>
+        <v>2255</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>A 2번 방 소품 묶음</t>
+          <t>B 4번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>R02A_ObjectsPoint</t>
+          <t>R04B_ObjectsPoint</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>13073</v>
+        <v>13081</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래 &gt; R02A. A 소품 전체가 프리팹 하나</t>
+          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래 &gt; R04B. B 소품 전체가 메시 하나인 프리팹. A 묶음과 같은 자리 (B 모델은 원래 z -6.5 옆방 자리지만 기준점이 A와 같은 상대 위치라 같은 앵커에 맞음)</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -4052,32 +4032,32 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2248</v>
+        <v>2257</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>B 2번 방 소품 · 액자 묶음</t>
+          <t>A 5번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>R02B_ObjectsPoint</t>
+          <t>R05A_ObjectsPoint</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>13074</v>
+        <v>13083</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_02_Structure &gt; R02_Structure &gt; R02_Points 아래 &gt; R02B. 액자 · 풀 등 B 소품 전체가 프리팹 하나</t>
+          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래 &gt; R05A. A 소품 전체가 프리팹 하나 (빈 루트 = 방 기준점, 안에 메시 Room_05_A_Objects). B 묶음과 같은 자리</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -4088,51 +4068,51 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2250</v>
+        <v>2258</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>3번 방 천장 (A·B 공통)</t>
+          <t>B 5번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>R03_CeilingPoint</t>
+          <t>R05B_ObjectsPoint</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>13076</v>
+        <v>13084</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래. 지금은 천장이 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.002를 지울 때 Y로</t>
+          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래 &gt; R05B. B 소품 전체가 프리팹 하나 (빈 루트 = 방 기준점, 안에 메시 Room_05_B_Objects를 +13 m 옮겨 A 방 자리에 맞춤). A 묶음과 같은 자리</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2251</v>
+        <v>2260</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>A 3번 방 소품 묶음</t>
+          <t>A 6번 방 소품 묶음</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -4141,15 +4121,15 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>R03A_ObjectsPoint</t>
+          <t>R06A_ObjectsPoint</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13077</v>
+        <v>13086</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래 &gt; R03A. A 소품 전체(조명 · 벽 무늬 · 문틀)가 프리팹 하나. B 묶음과 같은 자리</t>
+          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래 &gt; R06A. A 소품 전체가 메시 하나인 프리팹. 위치 · 회전은 모델 기준점 그대로 (방 중앙 바닥, X -90). B 묶음과 같은 자리</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -4160,15 +4140,15 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>2252</v>
+        <v>2261</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>B 3번 방 소품 묶음</t>
+          <t>B 6번 방 소품 · TV 묶음</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
@@ -4177,15 +4157,15 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>R03B_ObjectsPoint</t>
+          <t>R06B_ObjectsPoint</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>13078</v>
+        <v>13087</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_03_Structure &gt; R03_Structure &gt; R03_Points 아래 &gt; R03B. B 소품 전체가 프리팹 하나. A 묶음과 같은 자리 (B 모델은 원래 z -6.5에 있어 프리팹 안에서 +13 m 옮겨 A 방 자리에 맞춤)</t>
+          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래 &gt; R06B. B 소품과 TV 12대가 메시 하나인 프리팹 (TV 화면 자리 PZ_R6_B_TV_01~12 포함). A 묶음과 같은 자리 (B 모델은 원래 z -6.5 옆방 자리지만 기준점이 A와 같은 상대 위치라 같은 앵커에 맞음)</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -4196,15 +4176,15 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>2253</v>
+        <v>2262</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>4번 방 천장 (A·B 공통)</t>
+          <t>7번 방 소품 묶음 (A·B 공통)</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
@@ -4213,342 +4193,18 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>R04_CeilingPoint</t>
+          <t>R07_ObjectsPoint</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13079</v>
+        <v>13088</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래. 지금은 천장 Ceiling.003이 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.003을 지울 때 Y로</t>
+          <t>방 프리팹 R07_Structure &gt; R07_Points 아래. 걸레받이 · 천장 조명 · 문 옆 판이 메시 하나인 프리팹. 방 중앙 바닥 (-83, 0, 6.5), 회전 없음</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>2254</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>A 4번 방 소품 묶음</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>R04A_ObjectsPoint</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>13080</v>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래 &gt; R04A. A 소품 전체가 메시 하나인 프리팹. 위치 · 회전은 모델 기준점 그대로 (바닥 위 3.765 m, X -90). B 묶음과 같은 자리</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>2255</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 소품 묶음</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>R04B_ObjectsPoint</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>13081</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_04_Structure &gt; Room_04_A_Structure &gt; R04_Points 아래 &gt; R04B. B 소품 전체가 메시 하나인 프리팹. A 묶음과 같은 자리 (B 모델은 원래 z -6.5 옆방 자리지만 기준점이 A와 같은 상대 위치라 같은 앵커에 맞음)</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>2256</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>5번 방 천장 (A·B 공통)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>R05_CeilingPoint</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>13082</v>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래. 지금은 천장 Ceiling.004가 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.004를 지울 때 Y로</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>2257</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 소품 묶음</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>R05A_ObjectsPoint</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>13083</v>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래 &gt; R05A. A 소품 전체가 프리팹 하나 (빈 루트 = 방 기준점, 안에 메시 Room_05_A_Objects). B 묶음과 같은 자리</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>2258</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>B 5번 방 소품 묶음</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>R05B_ObjectsPoint</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>13084</v>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_05_Structure &gt; Room_05_A_Structure &gt; R05_Points 아래 &gt; R05B. B 소품 전체가 프리팹 하나 (빈 루트 = 방 기준점, 안에 메시 Room_05_B_Objects를 +13 m 옮겨 A 방 자리에 맞춤). A 묶음과 같은 자리</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>2259</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>6번 방 천장 (A·B 공통)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>R06_CeilingPoint</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>13085</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래. 지금은 천장 Ceiling.005가 방 프리팹 안에 그대로 있어서 꺼 둠 (켜면 천장이 두 겹). 방 프리팹의 Ceiling.005를 지울 때 Y로</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
-        <v>2260</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>A 6번 방 소품 묶음</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>R06A_ObjectsPoint</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>13086</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래 &gt; R06A. A 소품 전체가 메시 하나인 프리팹. 위치 · 회전은 모델 기준점 그대로 (방 중앙 바닥, X -90). B 묶음과 같은 자리</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n">
-        <v>2261</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 소품 · TV 묶음</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>R06B_ObjectsPoint</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>13087</v>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 SILENT_Room_06_A_Structure &gt; Room_06_A_WallsFloor_Merged &gt; R06_Points 아래 &gt; R06B. B 소품과 TV 12대가 메시 하나인 프리팹 (TV 화면 자리 PZ_R6_B_TV_01~12 포함). A 묶음과 같은 자리 (B 모델은 원래 z -6.5 옆방 자리지만 기준점이 A와 같은 상대 위치라 같은 앵커에 맞음)</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="n">
-        <v>2262</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>7번 방 소품 묶음 (A·B 공통)</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>R07_ObjectsPoint</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>13088</v>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>방 프리팹 R07_Structure &gt; R07_Points 아래. 걸레받이 · 천장 조명 · 문 옆 판이 메시 하나인 프리팹. 방 중앙 바닥 (-83, 0, 6.5), 회전 없음</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/EXCEL/SILENT_Room_Datatable.xlsx
+++ b/EXCEL/SILENT_Room_Datatable.xlsx
@@ -90,7 +90,7 @@
     <t>R01B_LEDPanelPoint</t>
   </si>
   <si>
-    <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01B 아래. 출구 문 위, 출구 문 위 바닥에서 2.73 m, 출구 벽 안쪽 면. 방 안쪽을 봄. COLOR_LETTER 7001 SignAnchor가 이 행을 가리킴</t>
+    <t>B만 출력. LED 표시판 R01_LEDPanel (PREFAB 13043, 글자 L). 방 프리팹 Room_01_Final &gt; R01_Structure &gt; R01_Points &gt; R01B 아래. 출구 문 위, 출구 문 위 바닥에서 2.73 m, 출구 벽 안쪽 면. 방 안쪽을 봄. COLOR_LETTER 7001 SignAnchor가 이 행을 가리킴</t>
   </si>
   <si>
     <t>Y</t>
@@ -126,7 +126,7 @@
     <t>R02A_LEDPanelPoint</t>
   </si>
   <si>
-    <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_02_Structure &gt; R02_Points &gt; R02A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7002 SignAnchor가 이 행을 가리킴</t>
+    <t>A만 출력. LED 표시판 R02_LEDPanel (PREFAB 13044). 방 프리팹 SILENT_Room_02_Structure &gt; R02_Points &gt; R02A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7002 SignAnchor가 이 행을 가리킴</t>
   </si>
   <si>
     <t>B 3번 방 글자 표시판</t>
@@ -135,7 +135,7 @@
     <t>R03B_LEDPanelPoint</t>
   </si>
   <si>
-    <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_03_Structure &gt; R03_Points &gt; R03B 아래. 출구 문 위, B 소품 묶음 안 PZ_R3_B_RewardDisplay 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7003 SignAnchor가 이 행을 가리킴</t>
+    <t>B만 출력. LED 표시판 R03_LEDPanel (PREFAB 13045). 방 프리팹 SILENT_Room_03_Structure &gt; R03_Points &gt; R03B 아래. 출구 문 위, B 소품 묶음 안 PZ_R3_B_RewardDisplay 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7003 SignAnchor가 이 행을 가리킴</t>
   </si>
   <si>
     <t>A 4번 방 글자 표시판</t>
@@ -144,7 +144,7 @@
     <t>R04A_LEDPanelPoint</t>
   </si>
   <si>
-    <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_04_Structure &gt; R04_Points &gt; R04A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7004 SignAnchor가 이 행을 가리킴</t>
+    <t>A만 출력. LED 표시판 R04_LEDPanel (PREFAB 13046). 방 프리팹 SILENT_Room_04_Structure &gt; R04_Points &gt; R04A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7004 SignAnchor가 이 행을 가리킴</t>
   </si>
   <si>
     <t>B 5번 방 글자 표시판</t>
@@ -153,7 +153,7 @@
     <t>R05B_LEDPanelPoint</t>
   </si>
   <si>
-    <t>B만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_05_Structure &gt; R05_Points &gt; R05B 아래. 출구 문 위, B 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7005 SignAnchor가 이 행을 가리킴</t>
+    <t>B만 출력. LED 표시판 R05_LEDPanel (PREFAB 13047). 방 프리팹 SILENT_Room_05_Structure &gt; R05_Points &gt; R05B 아래. 출구 문 위, B 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7005 SignAnchor가 이 행을 가리킴</t>
   </si>
   <si>
     <t>A 6번 방 글자 표시판</t>
@@ -162,7 +162,7 @@
     <t>R06A_LEDPanelPoint</t>
   </si>
   <si>
-    <t>A만 출력. 공용 LED 표시판 R01_LEDPanel. 방 프리팹 SILENT_Room_06_A_Structure &gt; R06_Points &gt; R06A 아래. 출구 문 위, A 소품 묶음 안 표시판 모양 바로 앞 (1 cm). 방 안쪽을 봄. COLOR_LETTER 7006 SignAnchor가 이 행을 가리킴</t>
+    <t>A만 출력. LED 표시판 R06_LEDPanel (PREFAB 13048). 방 프리팹 SILENT_Room_06_A_Structure &gt; R06_Points &gt; R06A 아래. 출구 문 위, 식물 벽 앞으로 50 cm 뺀 위치 (기존 표시판 모양은 식물에 묻혀 있음). 방 안쪽을 봄. COLOR_LETTER 7006 SignAnchor가 이 행을 가리킴</t>
   </si>
   <si>
     <t>2번 방 천장 (A·B 공통)</t>
@@ -3573,7 +3573,7 @@
         <v>32</v>
       </c>
       <c r="F10" s="8">
-        <v>13043</v>
+        <v>13044</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>33</v>
@@ -3599,7 +3599,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="8">
-        <v>13043</v>
+        <v>13045</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>36</v>
@@ -3625,7 +3625,7 @@
         <v>38</v>
       </c>
       <c r="F12" s="8">
-        <v>13043</v>
+        <v>13046</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>39</v>
@@ -3651,7 +3651,7 @@
         <v>41</v>
       </c>
       <c r="F13" s="8">
-        <v>13043</v>
+        <v>13047</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>42</v>
@@ -3677,7 +3677,7 @@
         <v>44</v>
       </c>
       <c r="F14" s="8">
-        <v>13043</v>
+        <v>13048</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>45</v>
